--- a/Paradigms/P0100_SpoutAssoc.xlsx
+++ b/Paradigms/P0100_SpoutAssoc.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="435">
   <si>
     <t>Object Definition</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Wall Definition</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Grid Size (x, y)</t>
@@ -1346,7 +1343,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1413,7 +1410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1438,9 +1435,6 @@
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1473,12 +1467,12 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1786,824 +1780,824 @@
   <dimension ref="A1:GU249"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="18" width="4.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="19" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="19" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="19" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="19" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="19" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="19" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="19" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="19" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="19" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="19" width="3.7192857142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="47" max="47" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="48" max="48" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="49" max="49" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="50" max="50" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="51" max="51" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="52" max="52" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="53" max="53" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="54" max="54" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="55" max="55" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="56" max="56" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="57" max="57" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="58" max="58" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="59" max="59" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="60" max="60" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="61" max="61" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="62" max="62" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="63" max="63" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="64" max="64" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="65" max="65" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="66" max="66" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="67" max="67" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="68" max="68" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="69" max="69" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="70" max="70" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="71" max="71" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="72" max="72" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="73" max="73" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="74" max="74" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="75" max="75" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="76" max="76" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="77" max="77" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="78" max="78" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="79" max="79" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="80" max="80" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="81" max="81" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="82" max="82" style="20" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="83" max="83" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="84" max="84" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="85" max="85" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="86" max="86" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="87" max="87" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="88" max="88" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="89" max="89" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="90" max="90" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="91" max="91" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="92" max="92" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="93" max="93" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="94" max="94" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="95" max="95" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="96" max="96" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="97" max="97" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="98" max="98" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="99" max="99" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="100" max="100" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="101" max="101" style="19" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="102" max="102" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="103" max="103" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="104" max="104" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="105" max="105" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="106" max="106" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="107" max="107" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="108" max="108" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="109" max="109" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="110" max="110" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="111" max="111" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="112" max="112" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="113" max="113" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="114" max="114" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="115" max="115" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="116" max="116" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="117" max="117" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="118" max="118" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="119" max="119" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="120" max="120" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="121" max="121" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="122" max="122" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="123" max="123" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="124" max="124" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="125" max="125" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="126" max="126" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="127" max="127" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="128" max="128" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="129" max="129" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="130" max="130" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="131" max="131" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="132" max="132" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="133" max="133" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="134" max="134" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="135" max="135" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="136" max="136" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="137" max="137" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="138" max="138" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="139" max="139" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="140" max="140" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="141" max="141" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="142" max="142" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="143" max="143" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="144" max="144" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="145" max="145" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="146" max="146" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="147" max="147" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="148" max="148" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="149" max="149" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="150" max="150" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="151" max="151" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="152" max="152" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="153" max="153" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="154" max="154" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="155" max="155" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="156" max="156" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="157" max="157" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="158" max="158" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="159" max="159" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="160" max="160" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="161" max="161" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="162" max="162" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="163" max="163" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="164" max="164" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="165" max="165" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="166" max="166" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="167" max="167" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="168" max="168" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="169" max="169" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="170" max="170" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="171" max="171" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="172" max="172" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="173" max="173" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="174" max="174" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="175" max="175" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="176" max="176" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="177" max="177" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="178" max="178" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="179" max="179" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="180" max="180" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="181" max="181" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="182" max="182" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="183" max="183" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="184" max="184" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="185" max="185" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="186" max="186" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="187" max="187" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="188" max="188" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="189" max="189" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="190" max="190" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="191" max="191" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="192" max="192" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="193" max="193" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="194" max="194" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="195" max="195" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="196" max="196" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="197" max="197" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="198" max="198" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="199" max="199" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="200" max="200" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="201" max="201" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="202" max="202" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="203" max="203" style="19" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="17" width="4.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="18" width="3.7192857142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="37" max="37" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="38" max="38" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="39" max="39" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="40" max="40" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="41" max="41" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="42" max="42" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="43" max="43" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="44" max="44" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="45" max="45" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="46" max="46" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="47" max="47" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="48" max="48" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="49" max="49" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="50" max="50" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="51" max="51" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="52" max="52" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="53" max="53" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="54" max="54" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="55" max="55" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="56" max="56" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="57" max="57" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="58" max="58" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="59" max="59" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="60" max="60" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="61" max="61" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="62" max="62" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="63" max="63" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="64" max="64" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="65" max="65" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="66" max="66" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="67" max="67" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="68" max="68" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="69" max="69" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="70" max="70" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="71" max="71" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="72" max="72" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="73" max="73" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="74" max="74" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="75" max="75" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="76" max="76" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="77" max="77" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="78" max="78" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="79" max="79" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="80" max="80" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="81" max="81" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="82" max="82" style="21" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="83" max="83" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="84" max="84" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="85" max="85" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="86" max="86" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="87" max="87" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="88" max="88" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="89" max="89" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="90" max="90" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="91" max="91" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="92" max="92" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="93" max="93" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="94" max="94" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="95" max="95" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="96" max="96" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="97" max="97" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="98" max="98" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="99" max="99" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="100" max="100" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="101" max="101" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="102" max="102" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="103" max="103" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="104" max="104" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="105" max="105" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="106" max="106" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="107" max="107" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="108" max="108" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="109" max="109" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="110" max="110" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="111" max="111" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="112" max="112" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="113" max="113" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="114" max="114" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="115" max="115" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="116" max="116" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="117" max="117" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="118" max="118" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="119" max="119" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="120" max="120" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="121" max="121" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="122" max="122" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="123" max="123" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="124" max="124" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="125" max="125" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="126" max="126" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="127" max="127" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="128" max="128" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="129" max="129" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="130" max="130" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="131" max="131" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="132" max="132" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="133" max="133" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="134" max="134" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="135" max="135" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="136" max="136" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="137" max="137" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="138" max="138" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="139" max="139" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="140" max="140" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="141" max="141" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="142" max="142" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="143" max="143" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="144" max="144" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="145" max="145" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="146" max="146" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="147" max="147" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="148" max="148" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="149" max="149" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="150" max="150" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="151" max="151" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="152" max="152" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="153" max="153" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="154" max="154" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="155" max="155" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="156" max="156" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="157" max="157" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="158" max="158" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="159" max="159" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="160" max="160" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="161" max="161" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="162" max="162" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="163" max="163" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="164" max="164" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="165" max="165" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="166" max="166" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="167" max="167" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="168" max="168" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="169" max="169" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="170" max="170" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="171" max="171" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="172" max="172" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="173" max="173" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="174" max="174" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="175" max="175" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="176" max="176" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="177" max="177" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="178" max="178" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="179" max="179" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="180" max="180" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="181" max="181" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="182" max="182" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="183" max="183" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="184" max="184" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="185" max="185" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="186" max="186" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="187" max="187" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="188" max="188" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="189" max="189" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="190" max="190" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="191" max="191" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="192" max="192" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="193" max="193" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="194" max="194" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="195" max="195" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="196" max="196" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="197" max="197" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="198" max="198" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="199" max="199" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="200" max="200" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="201" max="201" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="202" max="202" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="203" max="203" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="11"/>
-      <c r="B1" s="11" t="s">
+      <c r="A1" s="10"/>
+      <c r="B1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="N1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="P1" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="Q1" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="R1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="S1" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="T1" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="U1" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="V1" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="W1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="X1" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="Y1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Z1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="AA1" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AB1" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AC1" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AD1" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AE1" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AF1" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AG1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AH1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="AH1" s="11" t="s">
+      <c r="AI1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AI1" s="11" t="s">
+      <c r="AJ1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="AJ1" s="11" t="s">
+      <c r="AK1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="AK1" s="11" t="s">
+      <c r="AL1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="AL1" s="11" t="s">
+      <c r="AM1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="AM1" s="11" t="s">
+      <c r="AN1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="AN1" s="11" t="s">
+      <c r="AO1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AO1" s="11" t="s">
+      <c r="AP1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="AP1" s="11" t="s">
+      <c r="AQ1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="AQ1" s="11" t="s">
+      <c r="AR1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="AR1" s="11" t="s">
+      <c r="AS1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AS1" s="11" t="s">
+      <c r="AT1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="AT1" s="11" t="s">
+      <c r="AU1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="AU1" s="11" t="s">
+      <c r="AV1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AV1" s="11" t="s">
+      <c r="AW1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AW1" s="11" t="s">
+      <c r="AX1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AX1" s="11" t="s">
+      <c r="AY1" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="AY1" s="11" t="s">
+      <c r="AZ1" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="AZ1" s="11" t="s">
+      <c r="BA1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="BA1" s="11" t="s">
+      <c r="BB1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="BB1" s="11" t="s">
+      <c r="BC1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="BC1" s="11" t="s">
+      <c r="BD1" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="BD1" s="11" t="s">
+      <c r="BE1" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="BE1" s="11" t="s">
+      <c r="BF1" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="BF1" s="11" t="s">
+      <c r="BG1" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="BG1" s="11" t="s">
+      <c r="BH1" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="BH1" s="11" t="s">
+      <c r="BI1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="BI1" s="11" t="s">
+      <c r="BJ1" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="BJ1" s="11" t="s">
+      <c r="BK1" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="BK1" s="11" t="s">
+      <c r="BL1" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="BL1" s="11" t="s">
+      <c r="BM1" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="BM1" s="11" t="s">
+      <c r="BN1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="BN1" s="11" t="s">
+      <c r="BO1" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="BO1" s="11" t="s">
+      <c r="BP1" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="BP1" s="11" t="s">
+      <c r="BQ1" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="BQ1" s="11" t="s">
+      <c r="BR1" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="BR1" s="11" t="s">
+      <c r="BS1" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="BS1" s="11" t="s">
+      <c r="BT1" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="BT1" s="11" t="s">
+      <c r="BU1" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="BU1" s="11" t="s">
+      <c r="BV1" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="BV1" s="11" t="s">
+      <c r="BW1" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="BW1" s="11" t="s">
+      <c r="BX1" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="BX1" s="11" t="s">
+      <c r="BY1" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="BY1" s="11" t="s">
+      <c r="BZ1" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="BZ1" s="11" t="s">
+      <c r="CA1" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="CA1" s="11" t="s">
+      <c r="CB1" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="CB1" s="11" t="s">
+      <c r="CC1" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="CC1" s="11" t="s">
+      <c r="CD1" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="CD1" s="21" t="s">
+      <c r="CE1" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="CE1" s="11" t="s">
+      <c r="CF1" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="CF1" s="11" t="s">
+      <c r="CG1" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="CG1" s="11" t="s">
+      <c r="CH1" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="CH1" s="11" t="s">
+      <c r="CI1" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="CI1" s="11" t="s">
+      <c r="CJ1" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="CJ1" s="11" t="s">
+      <c r="CK1" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="CK1" s="11" t="s">
+      <c r="CL1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="CL1" s="11" t="s">
+      <c r="CM1" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="CM1" s="11" t="s">
+      <c r="CN1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="CN1" s="11" t="s">
+      <c r="CO1" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="CO1" s="11" t="s">
+      <c r="CP1" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="CP1" s="11" t="s">
+      <c r="CQ1" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="CQ1" s="11" t="s">
+      <c r="CR1" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="CR1" s="11" t="s">
+      <c r="CS1" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="CS1" s="11" t="s">
+      <c r="CT1" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="CT1" s="11" t="s">
+      <c r="CU1" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="CU1" s="11" t="s">
+      <c r="CV1" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="CV1" s="11" t="s">
+      <c r="CW1" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="CW1" s="11" t="s">
+      <c r="CX1" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="CX1" s="11" t="s">
+      <c r="CY1" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="CY1" s="11" t="s">
+      <c r="CZ1" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="CZ1" s="11" t="s">
+      <c r="DA1" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="DA1" s="11" t="s">
+      <c r="DB1" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="DB1" s="11" t="s">
+      <c r="DC1" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="DC1" s="11" t="s">
+      <c r="DD1" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="DD1" s="11" t="s">
+      <c r="DE1" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="DE1" s="11" t="s">
+      <c r="DF1" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="DF1" s="11" t="s">
+      <c r="DG1" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="DG1" s="11" t="s">
+      <c r="DH1" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="DH1" s="11" t="s">
+      <c r="DI1" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="DI1" s="11" t="s">
+      <c r="DJ1" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="DJ1" s="11" t="s">
+      <c r="DK1" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="DK1" s="11" t="s">
+      <c r="DL1" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="DL1" s="11" t="s">
+      <c r="DM1" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="DM1" s="11" t="s">
+      <c r="DN1" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="DN1" s="11" t="s">
+      <c r="DO1" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="DO1" s="11" t="s">
+      <c r="DP1" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="DP1" s="11" t="s">
+      <c r="DQ1" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="DQ1" s="11" t="s">
+      <c r="DR1" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="DR1" s="11" t="s">
+      <c r="DS1" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="DS1" s="11" t="s">
+      <c r="DT1" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="DT1" s="11" t="s">
+      <c r="DU1" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="DU1" s="11" t="s">
+      <c r="DV1" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="DV1" s="11" t="s">
+      <c r="DW1" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="DW1" s="11" t="s">
+      <c r="DX1" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="DX1" s="11" t="s">
+      <c r="DY1" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="DY1" s="11" t="s">
+      <c r="DZ1" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="DZ1" s="11" t="s">
+      <c r="EA1" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="EA1" s="11" t="s">
+      <c r="EB1" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="EB1" s="11" t="s">
+      <c r="EC1" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="EC1" s="11" t="s">
+      <c r="ED1" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="ED1" s="11" t="s">
+      <c r="EE1" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="EE1" s="11" t="s">
+      <c r="EF1" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="EF1" s="11" t="s">
+      <c r="EG1" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="EG1" s="11" t="s">
+      <c r="EH1" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="EH1" s="11" t="s">
+      <c r="EI1" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="EI1" s="11" t="s">
+      <c r="EJ1" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="EJ1" s="11" t="s">
+      <c r="EK1" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="EK1" s="11" t="s">
+      <c r="EL1" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="EL1" s="11" t="s">
+      <c r="EM1" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="EM1" s="11" t="s">
+      <c r="EN1" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="EN1" s="11" t="s">
+      <c r="EO1" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="EO1" s="11" t="s">
+      <c r="EP1" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="EP1" s="11" t="s">
+      <c r="EQ1" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="EQ1" s="11" t="s">
+      <c r="ER1" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="ER1" s="11" t="s">
+      <c r="ES1" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="ES1" s="11" t="s">
+      <c r="ET1" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="ET1" s="11" t="s">
+      <c r="EU1" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="EU1" s="11" t="s">
+      <c r="EV1" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="EV1" s="11" t="s">
+      <c r="EW1" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="EW1" s="11" t="s">
+      <c r="EX1" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="EX1" s="11" t="s">
+      <c r="EY1" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="EY1" s="11" t="s">
+      <c r="EZ1" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="EZ1" s="11" t="s">
+      <c r="FA1" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="FA1" s="11" t="s">
+      <c r="FB1" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="FB1" s="11" t="s">
+      <c r="FC1" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="FC1" s="11" t="s">
+      <c r="FD1" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="FD1" s="11" t="s">
+      <c r="FE1" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="FE1" s="11" t="s">
+      <c r="FF1" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="FF1" s="11" t="s">
+      <c r="FG1" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="FG1" s="11" t="s">
+      <c r="FH1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="FH1" s="11" t="s">
+      <c r="FI1" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="FI1" s="11" t="s">
+      <c r="FJ1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="FJ1" s="11" t="s">
+      <c r="FK1" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="FK1" s="11" t="s">
+      <c r="FL1" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="FL1" s="11" t="s">
+      <c r="FM1" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="FM1" s="11" t="s">
+      <c r="FN1" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="FN1" s="11" t="s">
+      <c r="FO1" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="FO1" s="11" t="s">
+      <c r="FP1" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="FP1" s="11" t="s">
+      <c r="FQ1" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="FQ1" s="11" t="s">
+      <c r="FR1" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="FR1" s="11" t="s">
+      <c r="FS1" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="FS1" s="11" t="s">
+      <c r="FT1" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="FT1" s="11" t="s">
+      <c r="FU1" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="FU1" s="11" t="s">
+      <c r="FV1" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="FV1" s="11" t="s">
+      <c r="FW1" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="FW1" s="11" t="s">
+      <c r="FX1" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="FX1" s="11" t="s">
+      <c r="FY1" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="FY1" s="11" t="s">
+      <c r="FZ1" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="FZ1" s="11" t="s">
+      <c r="GA1" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="GA1" s="11" t="s">
+      <c r="GB1" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="GB1" s="11" t="s">
+      <c r="GC1" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="GC1" s="11" t="s">
+      <c r="GD1" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="GD1" s="11" t="s">
+      <c r="GE1" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="GE1" s="11" t="s">
+      <c r="GF1" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="GF1" s="11" t="s">
+      <c r="GG1" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="GG1" s="11" t="s">
+      <c r="GH1" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="GH1" s="11" t="s">
+      <c r="GI1" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="GI1" s="11" t="s">
+      <c r="GJ1" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="GJ1" s="11" t="s">
+      <c r="GK1" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="GK1" s="11" t="s">
+      <c r="GL1" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="GL1" s="11" t="s">
+      <c r="GM1" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="GM1" s="11" t="s">
+      <c r="GN1" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="GN1" s="11" t="s">
+      <c r="GO1" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="GO1" s="11" t="s">
+      <c r="GP1" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="GP1" s="11" t="s">
+      <c r="GQ1" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="GQ1" s="11" t="s">
+      <c r="GR1" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="GR1" s="11" t="s">
+      <c r="GS1" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="GS1" s="11" t="s">
+      <c r="GT1" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="GT1" s="11" t="s">
+      <c r="GU1" s="10"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="GU1" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -2682,7 +2676,7 @@
       <c r="CA2" s="3"/>
       <c r="CB2" s="3"/>
       <c r="CC2" s="3"/>
-      <c r="CD2" s="15"/>
+      <c r="CD2" s="14"/>
       <c r="CE2" s="3"/>
       <c r="CF2" s="3"/>
       <c r="CG2" s="3"/>
@@ -2806,11 +2800,11 @@
       <c r="GU2" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="11" t="s">
-        <v>236</v>
+      <c r="A3" s="10" t="s">
+        <v>235</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -2889,7 +2883,7 @@
       <c r="CA3" s="3"/>
       <c r="CB3" s="3"/>
       <c r="CC3" s="3"/>
-      <c r="CD3" s="15"/>
+      <c r="CD3" s="14"/>
       <c r="CE3" s="3"/>
       <c r="CF3" s="3"/>
       <c r="CG3" s="3"/>
@@ -3013,8 +3007,8 @@
       <c r="GU3" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="11" t="s">
-        <v>237</v>
+      <c r="A4" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3096,7 +3090,7 @@
       <c r="CA4" s="3"/>
       <c r="CB4" s="3"/>
       <c r="CC4" s="3"/>
-      <c r="CD4" s="15"/>
+      <c r="CD4" s="14"/>
       <c r="CE4" s="3"/>
       <c r="CF4" s="3"/>
       <c r="CG4" s="3"/>
@@ -3220,8 +3214,8 @@
       <c r="GU4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="11" t="s">
-        <v>238</v>
+      <c r="A5" s="10" t="s">
+        <v>237</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3303,7 +3297,7 @@
       <c r="CA5" s="3"/>
       <c r="CB5" s="3"/>
       <c r="CC5" s="3"/>
-      <c r="CD5" s="15"/>
+      <c r="CD5" s="14"/>
       <c r="CE5" s="3"/>
       <c r="CF5" s="3"/>
       <c r="CG5" s="3"/>
@@ -3427,8 +3421,8 @@
       <c r="GU5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="11" t="s">
-        <v>239</v>
+      <c r="A6" s="10" t="s">
+        <v>238</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3510,7 +3504,7 @@
       <c r="CA6" s="3"/>
       <c r="CB6" s="3"/>
       <c r="CC6" s="3"/>
-      <c r="CD6" s="15"/>
+      <c r="CD6" s="14"/>
       <c r="CE6" s="3"/>
       <c r="CF6" s="3"/>
       <c r="CG6" s="3"/>
@@ -3634,8 +3628,8 @@
       <c r="GU6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="11" t="s">
-        <v>240</v>
+      <c r="A7" s="10" t="s">
+        <v>239</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -3717,7 +3711,7 @@
       <c r="CA7" s="3"/>
       <c r="CB7" s="3"/>
       <c r="CC7" s="3"/>
-      <c r="CD7" s="15"/>
+      <c r="CD7" s="14"/>
       <c r="CE7" s="3"/>
       <c r="CF7" s="3"/>
       <c r="CG7" s="3"/>
@@ -3841,8 +3835,8 @@
       <c r="GU7" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="11" t="s">
-        <v>241</v>
+      <c r="A8" s="10" t="s">
+        <v>240</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -3924,7 +3918,7 @@
       <c r="CA8" s="3"/>
       <c r="CB8" s="3"/>
       <c r="CC8" s="3"/>
-      <c r="CD8" s="15"/>
+      <c r="CD8" s="14"/>
       <c r="CE8" s="3"/>
       <c r="CF8" s="3"/>
       <c r="CG8" s="3"/>
@@ -4048,8 +4042,8 @@
       <c r="GU8" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="11" t="s">
-        <v>242</v>
+      <c r="A9" s="10" t="s">
+        <v>241</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4131,7 +4125,7 @@
       <c r="CA9" s="3"/>
       <c r="CB9" s="3"/>
       <c r="CC9" s="3"/>
-      <c r="CD9" s="15"/>
+      <c r="CD9" s="14"/>
       <c r="CE9" s="3"/>
       <c r="CF9" s="3"/>
       <c r="CG9" s="3"/>
@@ -4255,8 +4249,8 @@
       <c r="GU9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="11" t="s">
-        <v>243</v>
+      <c r="A10" s="10" t="s">
+        <v>242</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -4338,7 +4332,7 @@
       <c r="CA10" s="3"/>
       <c r="CB10" s="3"/>
       <c r="CC10" s="3"/>
-      <c r="CD10" s="15"/>
+      <c r="CD10" s="14"/>
       <c r="CE10" s="3"/>
       <c r="CF10" s="3"/>
       <c r="CG10" s="3"/>
@@ -4462,8 +4456,8 @@
       <c r="GU10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="11" t="s">
-        <v>244</v>
+      <c r="A11" s="10" t="s">
+        <v>243</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -4545,7 +4539,7 @@
       <c r="CA11" s="3"/>
       <c r="CB11" s="3"/>
       <c r="CC11" s="3"/>
-      <c r="CD11" s="15"/>
+      <c r="CD11" s="14"/>
       <c r="CE11" s="3"/>
       <c r="CF11" s="3"/>
       <c r="CG11" s="3"/>
@@ -4669,8 +4663,8 @@
       <c r="GU11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="11" t="s">
-        <v>245</v>
+      <c r="A12" s="10" t="s">
+        <v>244</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -4752,7 +4746,7 @@
       <c r="CA12" s="3"/>
       <c r="CB12" s="3"/>
       <c r="CC12" s="3"/>
-      <c r="CD12" s="15"/>
+      <c r="CD12" s="14"/>
       <c r="CE12" s="3"/>
       <c r="CF12" s="3"/>
       <c r="CG12" s="3"/>
@@ -4876,8 +4870,8 @@
       <c r="GU12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="11" t="s">
-        <v>246</v>
+      <c r="A13" s="10" t="s">
+        <v>245</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -4959,7 +4953,7 @@
       <c r="CA13" s="3"/>
       <c r="CB13" s="3"/>
       <c r="CC13" s="3"/>
-      <c r="CD13" s="15"/>
+      <c r="CD13" s="14"/>
       <c r="CE13" s="3"/>
       <c r="CF13" s="3"/>
       <c r="CG13" s="3"/>
@@ -5083,8 +5077,8 @@
       <c r="GU13" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="11" t="s">
-        <v>247</v>
+      <c r="A14" s="10" t="s">
+        <v>246</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -5166,7 +5160,7 @@
       <c r="CA14" s="3"/>
       <c r="CB14" s="3"/>
       <c r="CC14" s="3"/>
-      <c r="CD14" s="15"/>
+      <c r="CD14" s="14"/>
       <c r="CE14" s="3"/>
       <c r="CF14" s="3"/>
       <c r="CG14" s="3"/>
@@ -5290,8 +5284,8 @@
       <c r="GU14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="11" t="s">
-        <v>248</v>
+      <c r="A15" s="10" t="s">
+        <v>247</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5373,7 +5367,7 @@
       <c r="CA15" s="3"/>
       <c r="CB15" s="3"/>
       <c r="CC15" s="3"/>
-      <c r="CD15" s="15"/>
+      <c r="CD15" s="14"/>
       <c r="CE15" s="3"/>
       <c r="CF15" s="3"/>
       <c r="CG15" s="3"/>
@@ -5497,8 +5491,8 @@
       <c r="GU15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="11" t="s">
-        <v>249</v>
+      <c r="A16" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -5580,7 +5574,7 @@
       <c r="CA16" s="3"/>
       <c r="CB16" s="3"/>
       <c r="CC16" s="3"/>
-      <c r="CD16" s="15"/>
+      <c r="CD16" s="14"/>
       <c r="CE16" s="3"/>
       <c r="CF16" s="3"/>
       <c r="CG16" s="3"/>
@@ -5704,8 +5698,8 @@
       <c r="GU16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="11" t="s">
-        <v>250</v>
+      <c r="A17" s="10" t="s">
+        <v>249</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5787,7 +5781,7 @@
       <c r="CA17" s="3"/>
       <c r="CB17" s="3"/>
       <c r="CC17" s="3"/>
-      <c r="CD17" s="15"/>
+      <c r="CD17" s="14"/>
       <c r="CE17" s="3"/>
       <c r="CF17" s="3"/>
       <c r="CG17" s="3"/>
@@ -5911,8 +5905,8 @@
       <c r="GU17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="11" t="s">
-        <v>251</v>
+      <c r="A18" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -5994,7 +5988,7 @@
       <c r="CA18" s="3"/>
       <c r="CB18" s="3"/>
       <c r="CC18" s="3"/>
-      <c r="CD18" s="15"/>
+      <c r="CD18" s="14"/>
       <c r="CE18" s="3"/>
       <c r="CF18" s="3"/>
       <c r="CG18" s="3"/>
@@ -6118,8 +6112,8 @@
       <c r="GU18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="11" t="s">
-        <v>252</v>
+      <c r="A19" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -6201,7 +6195,7 @@
       <c r="CA19" s="3"/>
       <c r="CB19" s="3"/>
       <c r="CC19" s="3"/>
-      <c r="CD19" s="15"/>
+      <c r="CD19" s="14"/>
       <c r="CE19" s="3"/>
       <c r="CF19" s="3"/>
       <c r="CG19" s="3"/>
@@ -6325,8 +6319,8 @@
       <c r="GU19" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="11" t="s">
-        <v>253</v>
+      <c r="A20" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -6408,7 +6402,7 @@
       <c r="CA20" s="3"/>
       <c r="CB20" s="3"/>
       <c r="CC20" s="3"/>
-      <c r="CD20" s="15"/>
+      <c r="CD20" s="14"/>
       <c r="CE20" s="3"/>
       <c r="CF20" s="3"/>
       <c r="CG20" s="3"/>
@@ -6532,8 +6526,8 @@
       <c r="GU20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
-      <c r="A21" s="11" t="s">
-        <v>254</v>
+      <c r="A21" s="10" t="s">
+        <v>253</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -6615,7 +6609,7 @@
       <c r="CA21" s="3"/>
       <c r="CB21" s="3"/>
       <c r="CC21" s="3"/>
-      <c r="CD21" s="15"/>
+      <c r="CD21" s="14"/>
       <c r="CE21" s="3"/>
       <c r="CF21" s="3"/>
       <c r="CG21" s="3"/>
@@ -6739,8 +6733,8 @@
       <c r="GU21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="11" t="s">
-        <v>255</v>
+      <c r="A22" s="10" t="s">
+        <v>254</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -6822,7 +6816,7 @@
       <c r="CA22" s="3"/>
       <c r="CB22" s="3"/>
       <c r="CC22" s="3"/>
-      <c r="CD22" s="15"/>
+      <c r="CD22" s="14"/>
       <c r="CE22" s="3"/>
       <c r="CF22" s="3"/>
       <c r="CG22" s="3"/>
@@ -6946,8 +6940,8 @@
       <c r="GU22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="11" t="s">
-        <v>256</v>
+      <c r="A23" s="10" t="s">
+        <v>255</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -7029,7 +7023,7 @@
       <c r="CA23" s="3"/>
       <c r="CB23" s="3"/>
       <c r="CC23" s="3"/>
-      <c r="CD23" s="15"/>
+      <c r="CD23" s="14"/>
       <c r="CE23" s="3"/>
       <c r="CF23" s="3"/>
       <c r="CG23" s="3"/>
@@ -7153,8 +7147,8 @@
       <c r="GU23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="11" t="s">
-        <v>257</v>
+      <c r="A24" s="10" t="s">
+        <v>256</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -7236,7 +7230,7 @@
       <c r="CA24" s="3"/>
       <c r="CB24" s="3"/>
       <c r="CC24" s="3"/>
-      <c r="CD24" s="15"/>
+      <c r="CD24" s="14"/>
       <c r="CE24" s="3"/>
       <c r="CF24" s="3"/>
       <c r="CG24" s="3"/>
@@ -7360,8 +7354,8 @@
       <c r="GU24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
-      <c r="A25" s="11" t="s">
-        <v>258</v>
+      <c r="A25" s="10" t="s">
+        <v>257</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -7443,7 +7437,7 @@
       <c r="CA25" s="3"/>
       <c r="CB25" s="3"/>
       <c r="CC25" s="3"/>
-      <c r="CD25" s="15"/>
+      <c r="CD25" s="14"/>
       <c r="CE25" s="3"/>
       <c r="CF25" s="3"/>
       <c r="CG25" s="3"/>
@@ -7567,8 +7561,8 @@
       <c r="GU25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
-      <c r="A26" s="11" t="s">
-        <v>259</v>
+      <c r="A26" s="10" t="s">
+        <v>258</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -7650,7 +7644,7 @@
       <c r="CA26" s="3"/>
       <c r="CB26" s="3"/>
       <c r="CC26" s="3"/>
-      <c r="CD26" s="15"/>
+      <c r="CD26" s="14"/>
       <c r="CE26" s="3"/>
       <c r="CF26" s="3"/>
       <c r="CG26" s="3"/>
@@ -7774,8 +7768,8 @@
       <c r="GU26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
-      <c r="A27" s="11" t="s">
-        <v>260</v>
+      <c r="A27" s="10" t="s">
+        <v>259</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -7857,7 +7851,7 @@
       <c r="CA27" s="3"/>
       <c r="CB27" s="3"/>
       <c r="CC27" s="3"/>
-      <c r="CD27" s="15"/>
+      <c r="CD27" s="14"/>
       <c r="CE27" s="3"/>
       <c r="CF27" s="3"/>
       <c r="CG27" s="3"/>
@@ -7981,8 +7975,8 @@
       <c r="GU27" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="11" t="s">
-        <v>261</v>
+      <c r="A28" s="10" t="s">
+        <v>260</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -8064,7 +8058,7 @@
       <c r="CA28" s="3"/>
       <c r="CB28" s="3"/>
       <c r="CC28" s="3"/>
-      <c r="CD28" s="15"/>
+      <c r="CD28" s="14"/>
       <c r="CE28" s="3"/>
       <c r="CF28" s="3"/>
       <c r="CG28" s="3"/>
@@ -8188,8 +8182,8 @@
       <c r="GU28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
-      <c r="A29" s="11" t="s">
-        <v>262</v>
+      <c r="A29" s="10" t="s">
+        <v>261</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -8271,7 +8265,7 @@
       <c r="CA29" s="3"/>
       <c r="CB29" s="3"/>
       <c r="CC29" s="3"/>
-      <c r="CD29" s="15"/>
+      <c r="CD29" s="14"/>
       <c r="CE29" s="3"/>
       <c r="CF29" s="3"/>
       <c r="CG29" s="3"/>
@@ -8395,8 +8389,8 @@
       <c r="GU29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
-      <c r="A30" s="11" t="s">
-        <v>263</v>
+      <c r="A30" s="10" t="s">
+        <v>262</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -8478,7 +8472,7 @@
       <c r="CA30" s="3"/>
       <c r="CB30" s="3"/>
       <c r="CC30" s="3"/>
-      <c r="CD30" s="15"/>
+      <c r="CD30" s="14"/>
       <c r="CE30" s="3"/>
       <c r="CF30" s="3"/>
       <c r="CG30" s="3"/>
@@ -8602,8 +8596,8 @@
       <c r="GU30" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
-      <c r="A31" s="11" t="s">
-        <v>264</v>
+      <c r="A31" s="10" t="s">
+        <v>263</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -8685,7 +8679,7 @@
       <c r="CA31" s="3"/>
       <c r="CB31" s="3"/>
       <c r="CC31" s="3"/>
-      <c r="CD31" s="15"/>
+      <c r="CD31" s="14"/>
       <c r="CE31" s="3"/>
       <c r="CF31" s="3"/>
       <c r="CG31" s="3"/>
@@ -8809,8 +8803,8 @@
       <c r="GU31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
-      <c r="A32" s="11" t="s">
-        <v>265</v>
+      <c r="A32" s="10" t="s">
+        <v>264</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -8892,7 +8886,7 @@
       <c r="CA32" s="3"/>
       <c r="CB32" s="3"/>
       <c r="CC32" s="3"/>
-      <c r="CD32" s="15"/>
+      <c r="CD32" s="14"/>
       <c r="CE32" s="3"/>
       <c r="CF32" s="3"/>
       <c r="CG32" s="3"/>
@@ -9016,8 +9010,8 @@
       <c r="GU32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
-      <c r="A33" s="11" t="s">
-        <v>266</v>
+      <c r="A33" s="10" t="s">
+        <v>265</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -9099,7 +9093,7 @@
       <c r="CA33" s="3"/>
       <c r="CB33" s="3"/>
       <c r="CC33" s="3"/>
-      <c r="CD33" s="15"/>
+      <c r="CD33" s="14"/>
       <c r="CE33" s="3"/>
       <c r="CF33" s="3"/>
       <c r="CG33" s="3"/>
@@ -9223,8 +9217,8 @@
       <c r="GU33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
-      <c r="A34" s="11" t="s">
-        <v>267</v>
+      <c r="A34" s="10" t="s">
+        <v>266</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -9306,7 +9300,7 @@
       <c r="CA34" s="3"/>
       <c r="CB34" s="3"/>
       <c r="CC34" s="3"/>
-      <c r="CD34" s="15"/>
+      <c r="CD34" s="14"/>
       <c r="CE34" s="3"/>
       <c r="CF34" s="3"/>
       <c r="CG34" s="3"/>
@@ -9430,8 +9424,8 @@
       <c r="GU34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
-      <c r="A35" s="11" t="s">
-        <v>268</v>
+      <c r="A35" s="10" t="s">
+        <v>267</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -9513,7 +9507,7 @@
       <c r="CA35" s="3"/>
       <c r="CB35" s="3"/>
       <c r="CC35" s="3"/>
-      <c r="CD35" s="15"/>
+      <c r="CD35" s="14"/>
       <c r="CE35" s="3"/>
       <c r="CF35" s="3"/>
       <c r="CG35" s="3"/>
@@ -9637,8 +9631,8 @@
       <c r="GU35" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
-      <c r="A36" s="11" t="s">
-        <v>269</v>
+      <c r="A36" s="10" t="s">
+        <v>268</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -9720,7 +9714,7 @@
       <c r="CA36" s="3"/>
       <c r="CB36" s="3"/>
       <c r="CC36" s="3"/>
-      <c r="CD36" s="15"/>
+      <c r="CD36" s="14"/>
       <c r="CE36" s="3"/>
       <c r="CF36" s="3"/>
       <c r="CG36" s="3"/>
@@ -9844,8 +9838,8 @@
       <c r="GU36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
-      <c r="A37" s="11" t="s">
-        <v>270</v>
+      <c r="A37" s="10" t="s">
+        <v>269</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -9927,7 +9921,7 @@
       <c r="CA37" s="3"/>
       <c r="CB37" s="3"/>
       <c r="CC37" s="3"/>
-      <c r="CD37" s="15"/>
+      <c r="CD37" s="14"/>
       <c r="CE37" s="3"/>
       <c r="CF37" s="3"/>
       <c r="CG37" s="3"/>
@@ -10051,8 +10045,8 @@
       <c r="GU37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
-      <c r="A38" s="11" t="s">
-        <v>271</v>
+      <c r="A38" s="10" t="s">
+        <v>270</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -10134,7 +10128,7 @@
       <c r="CA38" s="3"/>
       <c r="CB38" s="3"/>
       <c r="CC38" s="3"/>
-      <c r="CD38" s="15"/>
+      <c r="CD38" s="14"/>
       <c r="CE38" s="3"/>
       <c r="CF38" s="3"/>
       <c r="CG38" s="3"/>
@@ -10258,8 +10252,8 @@
       <c r="GU38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
-      <c r="A39" s="11" t="s">
-        <v>272</v>
+      <c r="A39" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -10341,7 +10335,7 @@
       <c r="CA39" s="3"/>
       <c r="CB39" s="3"/>
       <c r="CC39" s="3"/>
-      <c r="CD39" s="15"/>
+      <c r="CD39" s="14"/>
       <c r="CE39" s="3"/>
       <c r="CF39" s="3"/>
       <c r="CG39" s="3"/>
@@ -10465,8 +10459,8 @@
       <c r="GU39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
-      <c r="A40" s="11" t="s">
-        <v>273</v>
+      <c r="A40" s="10" t="s">
+        <v>272</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -10548,7 +10542,7 @@
       <c r="CA40" s="3"/>
       <c r="CB40" s="3"/>
       <c r="CC40" s="3"/>
-      <c r="CD40" s="15"/>
+      <c r="CD40" s="14"/>
       <c r="CE40" s="3"/>
       <c r="CF40" s="3"/>
       <c r="CG40" s="3"/>
@@ -10672,8 +10666,8 @@
       <c r="GU40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
-      <c r="A41" s="11" t="s">
-        <v>274</v>
+      <c r="A41" s="10" t="s">
+        <v>273</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -10755,7 +10749,7 @@
       <c r="CA41" s="3"/>
       <c r="CB41" s="3"/>
       <c r="CC41" s="3"/>
-      <c r="CD41" s="15"/>
+      <c r="CD41" s="14"/>
       <c r="CE41" s="3"/>
       <c r="CF41" s="3"/>
       <c r="CG41" s="3"/>
@@ -10879,8 +10873,8 @@
       <c r="GU41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
-      <c r="A42" s="11" t="s">
-        <v>275</v>
+      <c r="A42" s="10" t="s">
+        <v>274</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -10962,7 +10956,7 @@
       <c r="CA42" s="3"/>
       <c r="CB42" s="3"/>
       <c r="CC42" s="3"/>
-      <c r="CD42" s="15"/>
+      <c r="CD42" s="14"/>
       <c r="CE42" s="3"/>
       <c r="CF42" s="3"/>
       <c r="CG42" s="3"/>
@@ -11086,8 +11080,8 @@
       <c r="GU42" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
-      <c r="A43" s="11" t="s">
-        <v>276</v>
+      <c r="A43" s="10" t="s">
+        <v>275</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -11169,7 +11163,7 @@
       <c r="CA43" s="3"/>
       <c r="CB43" s="3"/>
       <c r="CC43" s="3"/>
-      <c r="CD43" s="15"/>
+      <c r="CD43" s="14"/>
       <c r="CE43" s="3"/>
       <c r="CF43" s="3"/>
       <c r="CG43" s="3"/>
@@ -11293,8 +11287,8 @@
       <c r="GU43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
-      <c r="A44" s="11" t="s">
-        <v>277</v>
+      <c r="A44" s="10" t="s">
+        <v>276</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -11376,7 +11370,7 @@
       <c r="CA44" s="3"/>
       <c r="CB44" s="3"/>
       <c r="CC44" s="3"/>
-      <c r="CD44" s="15"/>
+      <c r="CD44" s="14"/>
       <c r="CE44" s="3"/>
       <c r="CF44" s="3"/>
       <c r="CG44" s="3"/>
@@ -11500,8 +11494,8 @@
       <c r="GU44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
-      <c r="A45" s="11" t="s">
-        <v>278</v>
+      <c r="A45" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -11583,7 +11577,7 @@
       <c r="CA45" s="3"/>
       <c r="CB45" s="3"/>
       <c r="CC45" s="3"/>
-      <c r="CD45" s="15"/>
+      <c r="CD45" s="14"/>
       <c r="CE45" s="3"/>
       <c r="CF45" s="3"/>
       <c r="CG45" s="3"/>
@@ -11707,8 +11701,8 @@
       <c r="GU45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
-      <c r="A46" s="11" t="s">
-        <v>279</v>
+      <c r="A46" s="10" t="s">
+        <v>278</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -11790,7 +11784,7 @@
       <c r="CA46" s="3"/>
       <c r="CB46" s="3"/>
       <c r="CC46" s="3"/>
-      <c r="CD46" s="15"/>
+      <c r="CD46" s="14"/>
       <c r="CE46" s="3"/>
       <c r="CF46" s="3"/>
       <c r="CG46" s="3"/>
@@ -11914,8 +11908,8 @@
       <c r="GU46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
-      <c r="A47" s="11" t="s">
-        <v>280</v>
+      <c r="A47" s="10" t="s">
+        <v>279</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -11997,7 +11991,7 @@
       <c r="CA47" s="3"/>
       <c r="CB47" s="3"/>
       <c r="CC47" s="3"/>
-      <c r="CD47" s="15"/>
+      <c r="CD47" s="14"/>
       <c r="CE47" s="3"/>
       <c r="CF47" s="3"/>
       <c r="CG47" s="3"/>
@@ -12121,8 +12115,8 @@
       <c r="GU47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
-      <c r="A48" s="11" t="s">
-        <v>281</v>
+      <c r="A48" s="10" t="s">
+        <v>280</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -12204,7 +12198,7 @@
       <c r="CA48" s="3"/>
       <c r="CB48" s="3"/>
       <c r="CC48" s="3"/>
-      <c r="CD48" s="15"/>
+      <c r="CD48" s="14"/>
       <c r="CE48" s="3"/>
       <c r="CF48" s="3"/>
       <c r="CG48" s="3"/>
@@ -12328,8 +12322,8 @@
       <c r="GU48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
-      <c r="A49" s="11" t="s">
-        <v>282</v>
+      <c r="A49" s="10" t="s">
+        <v>281</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -12411,7 +12405,7 @@
       <c r="CA49" s="3"/>
       <c r="CB49" s="3"/>
       <c r="CC49" s="3"/>
-      <c r="CD49" s="15"/>
+      <c r="CD49" s="14"/>
       <c r="CE49" s="3"/>
       <c r="CF49" s="3"/>
       <c r="CG49" s="3"/>
@@ -12535,8 +12529,8 @@
       <c r="GU49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
-      <c r="A50" s="11" t="s">
-        <v>283</v>
+      <c r="A50" s="10" t="s">
+        <v>282</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -12618,7 +12612,7 @@
       <c r="CA50" s="3"/>
       <c r="CB50" s="3"/>
       <c r="CC50" s="3"/>
-      <c r="CD50" s="15"/>
+      <c r="CD50" s="14"/>
       <c r="CE50" s="3"/>
       <c r="CF50" s="3"/>
       <c r="CG50" s="3"/>
@@ -12742,8 +12736,8 @@
       <c r="GU50" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
-      <c r="A51" s="11" t="s">
-        <v>284</v>
+      <c r="A51" s="10" t="s">
+        <v>283</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -12825,7 +12819,7 @@
       <c r="CA51" s="3"/>
       <c r="CB51" s="3"/>
       <c r="CC51" s="3"/>
-      <c r="CD51" s="15"/>
+      <c r="CD51" s="14"/>
       <c r="CE51" s="3"/>
       <c r="CF51" s="3"/>
       <c r="CG51" s="3"/>
@@ -12949,8 +12943,8 @@
       <c r="GU51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
-      <c r="A52" s="11" t="s">
-        <v>285</v>
+      <c r="A52" s="10" t="s">
+        <v>284</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -13032,7 +13026,7 @@
       <c r="CA52" s="3"/>
       <c r="CB52" s="3"/>
       <c r="CC52" s="3"/>
-      <c r="CD52" s="15"/>
+      <c r="CD52" s="14"/>
       <c r="CE52" s="3"/>
       <c r="CF52" s="3"/>
       <c r="CG52" s="3"/>
@@ -13156,8 +13150,8 @@
       <c r="GU52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
-      <c r="A53" s="11" t="s">
-        <v>286</v>
+      <c r="A53" s="10" t="s">
+        <v>285</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -13239,7 +13233,7 @@
       <c r="CA53" s="3"/>
       <c r="CB53" s="3"/>
       <c r="CC53" s="3"/>
-      <c r="CD53" s="15"/>
+      <c r="CD53" s="14"/>
       <c r="CE53" s="3"/>
       <c r="CF53" s="3"/>
       <c r="CG53" s="3"/>
@@ -13363,8 +13357,8 @@
       <c r="GU53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
-      <c r="A54" s="11" t="s">
-        <v>287</v>
+      <c r="A54" s="10" t="s">
+        <v>286</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -13446,7 +13440,7 @@
       <c r="CA54" s="3"/>
       <c r="CB54" s="3"/>
       <c r="CC54" s="3"/>
-      <c r="CD54" s="15"/>
+      <c r="CD54" s="14"/>
       <c r="CE54" s="3"/>
       <c r="CF54" s="3"/>
       <c r="CG54" s="3"/>
@@ -13570,8 +13564,8 @@
       <c r="GU54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
-      <c r="A55" s="11" t="s">
-        <v>288</v>
+      <c r="A55" s="10" t="s">
+        <v>287</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -13653,7 +13647,7 @@
       <c r="CA55" s="3"/>
       <c r="CB55" s="3"/>
       <c r="CC55" s="3"/>
-      <c r="CD55" s="15"/>
+      <c r="CD55" s="14"/>
       <c r="CE55" s="3"/>
       <c r="CF55" s="3"/>
       <c r="CG55" s="3"/>
@@ -13777,8 +13771,8 @@
       <c r="GU55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
-      <c r="A56" s="11" t="s">
-        <v>289</v>
+      <c r="A56" s="10" t="s">
+        <v>288</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -13860,7 +13854,7 @@
       <c r="CA56" s="3"/>
       <c r="CB56" s="3"/>
       <c r="CC56" s="3"/>
-      <c r="CD56" s="15"/>
+      <c r="CD56" s="14"/>
       <c r="CE56" s="3"/>
       <c r="CF56" s="3"/>
       <c r="CG56" s="3"/>
@@ -13984,8 +13978,8 @@
       <c r="GU56" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
-      <c r="A57" s="11" t="s">
-        <v>290</v>
+      <c r="A57" s="10" t="s">
+        <v>289</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -14067,7 +14061,7 @@
       <c r="CA57" s="3"/>
       <c r="CB57" s="3"/>
       <c r="CC57" s="3"/>
-      <c r="CD57" s="15"/>
+      <c r="CD57" s="14"/>
       <c r="CE57" s="3"/>
       <c r="CF57" s="3"/>
       <c r="CG57" s="3"/>
@@ -14191,8 +14185,8 @@
       <c r="GU57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
-      <c r="A58" s="11" t="s">
-        <v>291</v>
+      <c r="A58" s="10" t="s">
+        <v>290</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -14274,7 +14268,7 @@
       <c r="CA58" s="3"/>
       <c r="CB58" s="3"/>
       <c r="CC58" s="3"/>
-      <c r="CD58" s="15"/>
+      <c r="CD58" s="14"/>
       <c r="CE58" s="3"/>
       <c r="CF58" s="3"/>
       <c r="CG58" s="3"/>
@@ -14398,8 +14392,8 @@
       <c r="GU58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
-      <c r="A59" s="11" t="s">
-        <v>292</v>
+      <c r="A59" s="10" t="s">
+        <v>291</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -14481,7 +14475,7 @@
       <c r="CA59" s="3"/>
       <c r="CB59" s="3"/>
       <c r="CC59" s="3"/>
-      <c r="CD59" s="15"/>
+      <c r="CD59" s="14"/>
       <c r="CE59" s="3"/>
       <c r="CF59" s="3"/>
       <c r="CG59" s="3"/>
@@ -14605,8 +14599,8 @@
       <c r="GU59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
-      <c r="A60" s="11" t="s">
-        <v>293</v>
+      <c r="A60" s="10" t="s">
+        <v>292</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -14688,7 +14682,7 @@
       <c r="CA60" s="3"/>
       <c r="CB60" s="3"/>
       <c r="CC60" s="3"/>
-      <c r="CD60" s="15"/>
+      <c r="CD60" s="14"/>
       <c r="CE60" s="3"/>
       <c r="CF60" s="3"/>
       <c r="CG60" s="3"/>
@@ -14812,8 +14806,8 @@
       <c r="GU60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
-      <c r="A61" s="11" t="s">
-        <v>294</v>
+      <c r="A61" s="10" t="s">
+        <v>293</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -14895,7 +14889,7 @@
       <c r="CA61" s="3"/>
       <c r="CB61" s="3"/>
       <c r="CC61" s="3"/>
-      <c r="CD61" s="15"/>
+      <c r="CD61" s="14"/>
       <c r="CE61" s="3"/>
       <c r="CF61" s="3"/>
       <c r="CG61" s="3"/>
@@ -15019,8 +15013,8 @@
       <c r="GU61" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
-      <c r="A62" s="11" t="s">
-        <v>295</v>
+      <c r="A62" s="10" t="s">
+        <v>294</v>
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -15102,7 +15096,7 @@
       <c r="CA62" s="3"/>
       <c r="CB62" s="3"/>
       <c r="CC62" s="3"/>
-      <c r="CD62" s="15"/>
+      <c r="CD62" s="14"/>
       <c r="CE62" s="3"/>
       <c r="CF62" s="3"/>
       <c r="CG62" s="3"/>
@@ -15226,8 +15220,8 @@
       <c r="GU62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
-      <c r="A63" s="11" t="s">
-        <v>296</v>
+      <c r="A63" s="10" t="s">
+        <v>295</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -15309,7 +15303,7 @@
       <c r="CA63" s="3"/>
       <c r="CB63" s="3"/>
       <c r="CC63" s="3"/>
-      <c r="CD63" s="15"/>
+      <c r="CD63" s="14"/>
       <c r="CE63" s="3"/>
       <c r="CF63" s="3"/>
       <c r="CG63" s="3"/>
@@ -15433,8 +15427,8 @@
       <c r="GU63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
-      <c r="A64" s="11" t="s">
-        <v>297</v>
+      <c r="A64" s="10" t="s">
+        <v>296</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -15516,7 +15510,7 @@
       <c r="CA64" s="3"/>
       <c r="CB64" s="3"/>
       <c r="CC64" s="3"/>
-      <c r="CD64" s="15"/>
+      <c r="CD64" s="14"/>
       <c r="CE64" s="3"/>
       <c r="CF64" s="3"/>
       <c r="CG64" s="3"/>
@@ -15640,8 +15634,8 @@
       <c r="GU64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
-      <c r="A65" s="11" t="s">
-        <v>298</v>
+      <c r="A65" s="10" t="s">
+        <v>297</v>
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -15723,7 +15717,7 @@
       <c r="CA65" s="3"/>
       <c r="CB65" s="3"/>
       <c r="CC65" s="3"/>
-      <c r="CD65" s="15"/>
+      <c r="CD65" s="14"/>
       <c r="CE65" s="3"/>
       <c r="CF65" s="3"/>
       <c r="CG65" s="3"/>
@@ -15847,8 +15841,8 @@
       <c r="GU65" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
-      <c r="A66" s="11" t="s">
-        <v>299</v>
+      <c r="A66" s="10" t="s">
+        <v>298</v>
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -15930,7 +15924,7 @@
       <c r="CA66" s="3"/>
       <c r="CB66" s="3"/>
       <c r="CC66" s="3"/>
-      <c r="CD66" s="15"/>
+      <c r="CD66" s="14"/>
       <c r="CE66" s="3"/>
       <c r="CF66" s="3"/>
       <c r="CG66" s="3"/>
@@ -16054,8 +16048,8 @@
       <c r="GU66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
-      <c r="A67" s="11" t="s">
-        <v>300</v>
+      <c r="A67" s="10" t="s">
+        <v>299</v>
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -16137,7 +16131,7 @@
       <c r="CA67" s="3"/>
       <c r="CB67" s="3"/>
       <c r="CC67" s="3"/>
-      <c r="CD67" s="15"/>
+      <c r="CD67" s="14"/>
       <c r="CE67" s="3"/>
       <c r="CF67" s="3"/>
       <c r="CG67" s="3"/>
@@ -16261,8 +16255,8 @@
       <c r="GU67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
-      <c r="A68" s="11" t="s">
-        <v>301</v>
+      <c r="A68" s="10" t="s">
+        <v>300</v>
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -16344,7 +16338,7 @@
       <c r="CA68" s="3"/>
       <c r="CB68" s="3"/>
       <c r="CC68" s="3"/>
-      <c r="CD68" s="15"/>
+      <c r="CD68" s="14"/>
       <c r="CE68" s="3"/>
       <c r="CF68" s="3"/>
       <c r="CG68" s="3"/>
@@ -16468,8 +16462,8 @@
       <c r="GU68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5">
-      <c r="A69" s="11" t="s">
-        <v>302</v>
+      <c r="A69" s="10" t="s">
+        <v>301</v>
       </c>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -16551,7 +16545,7 @@
       <c r="CA69" s="3"/>
       <c r="CB69" s="3"/>
       <c r="CC69" s="3"/>
-      <c r="CD69" s="15"/>
+      <c r="CD69" s="14"/>
       <c r="CE69" s="3"/>
       <c r="CF69" s="3"/>
       <c r="CG69" s="3"/>
@@ -16675,8 +16669,8 @@
       <c r="GU69" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
-      <c r="A70" s="11" t="s">
-        <v>303</v>
+      <c r="A70" s="10" t="s">
+        <v>302</v>
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -16758,7 +16752,7 @@
       <c r="CA70" s="3"/>
       <c r="CB70" s="3"/>
       <c r="CC70" s="3"/>
-      <c r="CD70" s="15"/>
+      <c r="CD70" s="14"/>
       <c r="CE70" s="3"/>
       <c r="CF70" s="3"/>
       <c r="CG70" s="3"/>
@@ -16882,8 +16876,8 @@
       <c r="GU70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
-      <c r="A71" s="11" t="s">
-        <v>304</v>
+      <c r="A71" s="10" t="s">
+        <v>303</v>
       </c>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -16965,7 +16959,7 @@
       <c r="CA71" s="3"/>
       <c r="CB71" s="3"/>
       <c r="CC71" s="3"/>
-      <c r="CD71" s="15"/>
+      <c r="CD71" s="14"/>
       <c r="CE71" s="3"/>
       <c r="CF71" s="3"/>
       <c r="CG71" s="3"/>
@@ -17089,8 +17083,8 @@
       <c r="GU71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
-      <c r="A72" s="11" t="s">
-        <v>305</v>
+      <c r="A72" s="10" t="s">
+        <v>304</v>
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -17172,7 +17166,7 @@
       <c r="CA72" s="3"/>
       <c r="CB72" s="3"/>
       <c r="CC72" s="3"/>
-      <c r="CD72" s="15"/>
+      <c r="CD72" s="14"/>
       <c r="CE72" s="3"/>
       <c r="CF72" s="3"/>
       <c r="CG72" s="3"/>
@@ -17296,8 +17290,8 @@
       <c r="GU72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
-      <c r="A73" s="11" t="s">
-        <v>306</v>
+      <c r="A73" s="10" t="s">
+        <v>305</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -17379,7 +17373,7 @@
       <c r="CA73" s="3"/>
       <c r="CB73" s="3"/>
       <c r="CC73" s="3"/>
-      <c r="CD73" s="15"/>
+      <c r="CD73" s="14"/>
       <c r="CE73" s="3"/>
       <c r="CF73" s="3"/>
       <c r="CG73" s="3"/>
@@ -17503,8 +17497,8 @@
       <c r="GU73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
-      <c r="A74" s="11" t="s">
-        <v>307</v>
+      <c r="A74" s="10" t="s">
+        <v>306</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -17586,7 +17580,7 @@
       <c r="CA74" s="3"/>
       <c r="CB74" s="3"/>
       <c r="CC74" s="3"/>
-      <c r="CD74" s="15"/>
+      <c r="CD74" s="14"/>
       <c r="CE74" s="3"/>
       <c r="CF74" s="3"/>
       <c r="CG74" s="3"/>
@@ -17710,8 +17704,8 @@
       <c r="GU74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
-      <c r="A75" s="11" t="s">
-        <v>308</v>
+      <c r="A75" s="10" t="s">
+        <v>307</v>
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -17793,7 +17787,7 @@
       <c r="CA75" s="3"/>
       <c r="CB75" s="3"/>
       <c r="CC75" s="3"/>
-      <c r="CD75" s="15"/>
+      <c r="CD75" s="14"/>
       <c r="CE75" s="3"/>
       <c r="CF75" s="3"/>
       <c r="CG75" s="3"/>
@@ -17917,8 +17911,8 @@
       <c r="GU75" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
-      <c r="A76" s="11" t="s">
-        <v>309</v>
+      <c r="A76" s="10" t="s">
+        <v>308</v>
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -18000,7 +17994,7 @@
       <c r="CA76" s="3"/>
       <c r="CB76" s="3"/>
       <c r="CC76" s="3"/>
-      <c r="CD76" s="15"/>
+      <c r="CD76" s="14"/>
       <c r="CE76" s="3"/>
       <c r="CF76" s="3"/>
       <c r="CG76" s="3"/>
@@ -18124,8 +18118,8 @@
       <c r="GU76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
-      <c r="A77" s="11" t="s">
-        <v>310</v>
+      <c r="A77" s="10" t="s">
+        <v>309</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -18207,7 +18201,7 @@
       <c r="CA77" s="3"/>
       <c r="CB77" s="3"/>
       <c r="CC77" s="3"/>
-      <c r="CD77" s="15"/>
+      <c r="CD77" s="14"/>
       <c r="CE77" s="3"/>
       <c r="CF77" s="3"/>
       <c r="CG77" s="3"/>
@@ -18331,8 +18325,8 @@
       <c r="GU77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
-      <c r="A78" s="11" t="s">
-        <v>311</v>
+      <c r="A78" s="10" t="s">
+        <v>310</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -18414,7 +18408,7 @@
       <c r="CA78" s="3"/>
       <c r="CB78" s="3"/>
       <c r="CC78" s="3"/>
-      <c r="CD78" s="15"/>
+      <c r="CD78" s="14"/>
       <c r="CE78" s="3"/>
       <c r="CF78" s="3"/>
       <c r="CG78" s="3"/>
@@ -18538,8 +18532,8 @@
       <c r="GU78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
-      <c r="A79" s="11" t="s">
-        <v>312</v>
+      <c r="A79" s="10" t="s">
+        <v>311</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -18621,7 +18615,7 @@
       <c r="CA79" s="3"/>
       <c r="CB79" s="3"/>
       <c r="CC79" s="3"/>
-      <c r="CD79" s="15"/>
+      <c r="CD79" s="14"/>
       <c r="CE79" s="3"/>
       <c r="CF79" s="3"/>
       <c r="CG79" s="3"/>
@@ -18745,8 +18739,8 @@
       <c r="GU79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
-      <c r="A80" s="11" t="s">
-        <v>313</v>
+      <c r="A80" s="10" t="s">
+        <v>312</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -18828,7 +18822,7 @@
       <c r="CA80" s="3"/>
       <c r="CB80" s="3"/>
       <c r="CC80" s="3"/>
-      <c r="CD80" s="15"/>
+      <c r="CD80" s="14"/>
       <c r="CE80" s="3"/>
       <c r="CF80" s="3"/>
       <c r="CG80" s="3"/>
@@ -18952,8 +18946,8 @@
       <c r="GU80" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
-      <c r="A81" s="11" t="s">
-        <v>314</v>
+      <c r="A81" s="10" t="s">
+        <v>313</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -19035,7 +19029,7 @@
       <c r="CA81" s="3"/>
       <c r="CB81" s="3"/>
       <c r="CC81" s="3"/>
-      <c r="CD81" s="15"/>
+      <c r="CD81" s="14"/>
       <c r="CE81" s="3"/>
       <c r="CF81" s="3"/>
       <c r="CG81" s="3"/>
@@ -19159,8 +19153,8 @@
       <c r="GU81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
-      <c r="A82" s="11" t="s">
-        <v>315</v>
+      <c r="A82" s="10" t="s">
+        <v>314</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -19242,7 +19236,7 @@
       <c r="CA82" s="3"/>
       <c r="CB82" s="3"/>
       <c r="CC82" s="3"/>
-      <c r="CD82" s="15"/>
+      <c r="CD82" s="14"/>
       <c r="CE82" s="3"/>
       <c r="CF82" s="3"/>
       <c r="CG82" s="3"/>
@@ -19366,8 +19360,8 @@
       <c r="GU82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
-      <c r="A83" s="11" t="s">
-        <v>316</v>
+      <c r="A83" s="10" t="s">
+        <v>315</v>
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -19449,7 +19443,7 @@
       <c r="CA83" s="3"/>
       <c r="CB83" s="3"/>
       <c r="CC83" s="3"/>
-      <c r="CD83" s="15"/>
+      <c r="CD83" s="14"/>
       <c r="CE83" s="3"/>
       <c r="CF83" s="3"/>
       <c r="CG83" s="3"/>
@@ -19573,8 +19567,8 @@
       <c r="GU83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
-      <c r="A84" s="11" t="s">
-        <v>317</v>
+      <c r="A84" s="10" t="s">
+        <v>316</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -19656,7 +19650,7 @@
       <c r="CA84" s="3"/>
       <c r="CB84" s="3"/>
       <c r="CC84" s="3"/>
-      <c r="CD84" s="15"/>
+      <c r="CD84" s="14"/>
       <c r="CE84" s="3"/>
       <c r="CF84" s="3"/>
       <c r="CG84" s="3"/>
@@ -19780,8 +19774,8 @@
       <c r="GU84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
-      <c r="A85" s="11" t="s">
-        <v>318</v>
+      <c r="A85" s="10" t="s">
+        <v>317</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -19863,7 +19857,7 @@
       <c r="CA85" s="3"/>
       <c r="CB85" s="3"/>
       <c r="CC85" s="3"/>
-      <c r="CD85" s="15"/>
+      <c r="CD85" s="14"/>
       <c r="CE85" s="3"/>
       <c r="CF85" s="3"/>
       <c r="CG85" s="3"/>
@@ -19987,8 +19981,8 @@
       <c r="GU85" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
-      <c r="A86" s="11" t="s">
-        <v>319</v>
+      <c r="A86" s="10" t="s">
+        <v>318</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -20070,7 +20064,7 @@
       <c r="CA86" s="3"/>
       <c r="CB86" s="3"/>
       <c r="CC86" s="3"/>
-      <c r="CD86" s="15"/>
+      <c r="CD86" s="14"/>
       <c r="CE86" s="3"/>
       <c r="CF86" s="3"/>
       <c r="CG86" s="3"/>
@@ -20194,8 +20188,8 @@
       <c r="GU86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
-      <c r="A87" s="11" t="s">
-        <v>320</v>
+      <c r="A87" s="10" t="s">
+        <v>319</v>
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -20277,7 +20271,7 @@
       <c r="CA87" s="3"/>
       <c r="CB87" s="3"/>
       <c r="CC87" s="3"/>
-      <c r="CD87" s="15"/>
+      <c r="CD87" s="14"/>
       <c r="CE87" s="3"/>
       <c r="CF87" s="3"/>
       <c r="CG87" s="3"/>
@@ -20401,8 +20395,8 @@
       <c r="GU87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
-      <c r="A88" s="11" t="s">
-        <v>321</v>
+      <c r="A88" s="10" t="s">
+        <v>320</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -20484,7 +20478,7 @@
       <c r="CA88" s="3"/>
       <c r="CB88" s="3"/>
       <c r="CC88" s="3"/>
-      <c r="CD88" s="15"/>
+      <c r="CD88" s="14"/>
       <c r="CE88" s="3"/>
       <c r="CF88" s="3"/>
       <c r="CG88" s="3"/>
@@ -20608,8 +20602,8 @@
       <c r="GU88" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
-      <c r="A89" s="11" t="s">
-        <v>322</v>
+      <c r="A89" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -20691,7 +20685,7 @@
       <c r="CA89" s="3"/>
       <c r="CB89" s="3"/>
       <c r="CC89" s="3"/>
-      <c r="CD89" s="15"/>
+      <c r="CD89" s="14"/>
       <c r="CE89" s="3"/>
       <c r="CF89" s="3"/>
       <c r="CG89" s="3"/>
@@ -20815,8 +20809,8 @@
       <c r="GU89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
-      <c r="A90" s="11" t="s">
-        <v>323</v>
+      <c r="A90" s="10" t="s">
+        <v>322</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -20898,7 +20892,7 @@
       <c r="CA90" s="3"/>
       <c r="CB90" s="3"/>
       <c r="CC90" s="3"/>
-      <c r="CD90" s="15"/>
+      <c r="CD90" s="14"/>
       <c r="CE90" s="3"/>
       <c r="CF90" s="3"/>
       <c r="CG90" s="3"/>
@@ -21022,8 +21016,8 @@
       <c r="GU90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
-      <c r="A91" s="11" t="s">
-        <v>324</v>
+      <c r="A91" s="10" t="s">
+        <v>323</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -21105,7 +21099,7 @@
       <c r="CA91" s="3"/>
       <c r="CB91" s="3"/>
       <c r="CC91" s="3"/>
-      <c r="CD91" s="15"/>
+      <c r="CD91" s="14"/>
       <c r="CE91" s="3"/>
       <c r="CF91" s="3"/>
       <c r="CG91" s="3"/>
@@ -21229,8 +21223,8 @@
       <c r="GU91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
-      <c r="A92" s="11" t="s">
-        <v>325</v>
+      <c r="A92" s="10" t="s">
+        <v>324</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -21312,7 +21306,7 @@
       <c r="CA92" s="3"/>
       <c r="CB92" s="3"/>
       <c r="CC92" s="3"/>
-      <c r="CD92" s="15"/>
+      <c r="CD92" s="14"/>
       <c r="CE92" s="3"/>
       <c r="CF92" s="3"/>
       <c r="CG92" s="3"/>
@@ -21436,8 +21430,8 @@
       <c r="GU92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
-      <c r="A93" s="11" t="s">
-        <v>326</v>
+      <c r="A93" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -21519,7 +21513,7 @@
       <c r="CA93" s="3"/>
       <c r="CB93" s="3"/>
       <c r="CC93" s="3"/>
-      <c r="CD93" s="15"/>
+      <c r="CD93" s="14"/>
       <c r="CE93" s="3"/>
       <c r="CF93" s="3"/>
       <c r="CG93" s="3"/>
@@ -21643,8 +21637,8 @@
       <c r="GU93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
-      <c r="A94" s="11" t="s">
-        <v>327</v>
+      <c r="A94" s="10" t="s">
+        <v>326</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -21726,7 +21720,7 @@
       <c r="CA94" s="3"/>
       <c r="CB94" s="3"/>
       <c r="CC94" s="3"/>
-      <c r="CD94" s="15"/>
+      <c r="CD94" s="14"/>
       <c r="CE94" s="3"/>
       <c r="CF94" s="3"/>
       <c r="CG94" s="3"/>
@@ -21850,8 +21844,8 @@
       <c r="GU94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
-      <c r="A95" s="11" t="s">
-        <v>328</v>
+      <c r="A95" s="10" t="s">
+        <v>327</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -21933,7 +21927,7 @@
       <c r="CA95" s="3"/>
       <c r="CB95" s="3"/>
       <c r="CC95" s="3"/>
-      <c r="CD95" s="15"/>
+      <c r="CD95" s="14"/>
       <c r="CE95" s="3"/>
       <c r="CF95" s="3"/>
       <c r="CG95" s="3"/>
@@ -22057,8 +22051,8 @@
       <c r="GU95" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="19.5">
-      <c r="A96" s="11" t="s">
-        <v>329</v>
+      <c r="A96" s="10" t="s">
+        <v>328</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -22140,7 +22134,7 @@
       <c r="CA96" s="3"/>
       <c r="CB96" s="3"/>
       <c r="CC96" s="3"/>
-      <c r="CD96" s="15"/>
+      <c r="CD96" s="14"/>
       <c r="CE96" s="3"/>
       <c r="CF96" s="3"/>
       <c r="CG96" s="3"/>
@@ -22264,8 +22258,8 @@
       <c r="GU96" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="19.5">
-      <c r="A97" s="11" t="s">
-        <v>330</v>
+      <c r="A97" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -22347,7 +22341,7 @@
       <c r="CA97" s="3"/>
       <c r="CB97" s="3"/>
       <c r="CC97" s="3"/>
-      <c r="CD97" s="15"/>
+      <c r="CD97" s="14"/>
       <c r="CE97" s="3"/>
       <c r="CF97" s="3"/>
       <c r="CG97" s="3"/>
@@ -22471,8 +22465,8 @@
       <c r="GU97" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="19.5">
-      <c r="A98" s="11" t="s">
-        <v>331</v>
+      <c r="A98" s="10" t="s">
+        <v>330</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -22554,7 +22548,7 @@
       <c r="CA98" s="3"/>
       <c r="CB98" s="3"/>
       <c r="CC98" s="3"/>
-      <c r="CD98" s="15"/>
+      <c r="CD98" s="14"/>
       <c r="CE98" s="3"/>
       <c r="CF98" s="3"/>
       <c r="CG98" s="3"/>
@@ -22678,8 +22672,8 @@
       <c r="GU98" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="19.5">
-      <c r="A99" s="11" t="s">
-        <v>332</v>
+      <c r="A99" s="10" t="s">
+        <v>331</v>
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -22761,7 +22755,7 @@
       <c r="CA99" s="3"/>
       <c r="CB99" s="3"/>
       <c r="CC99" s="3"/>
-      <c r="CD99" s="15"/>
+      <c r="CD99" s="14"/>
       <c r="CE99" s="3"/>
       <c r="CF99" s="3"/>
       <c r="CG99" s="3"/>
@@ -22885,8 +22879,8 @@
       <c r="GU99" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="19.5">
-      <c r="A100" s="11" t="s">
-        <v>333</v>
+      <c r="A100" s="10" t="s">
+        <v>332</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -22968,7 +22962,7 @@
       <c r="CA100" s="3"/>
       <c r="CB100" s="3"/>
       <c r="CC100" s="3"/>
-      <c r="CD100" s="22"/>
+      <c r="CD100" s="20"/>
       <c r="CE100" s="3"/>
       <c r="CF100" s="3"/>
       <c r="CG100" s="3"/>
@@ -23092,8 +23086,8 @@
       <c r="GU100" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="19.5">
-      <c r="A101" s="11" t="s">
-        <v>334</v>
+      <c r="A101" s="10" t="s">
+        <v>333</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -23175,7 +23169,7 @@
       <c r="CA101" s="3"/>
       <c r="CB101" s="3"/>
       <c r="CC101" s="3"/>
-      <c r="CD101" s="15"/>
+      <c r="CD101" s="14"/>
       <c r="CE101" s="3"/>
       <c r="CF101" s="3"/>
       <c r="CG101" s="3"/>
@@ -23299,8 +23293,8 @@
       <c r="GU101" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="19.5">
-      <c r="A102" s="11" t="s">
-        <v>335</v>
+      <c r="A102" s="10" t="s">
+        <v>334</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -23382,7 +23376,7 @@
       <c r="CA102" s="3"/>
       <c r="CB102" s="3"/>
       <c r="CC102" s="3"/>
-      <c r="CD102" s="15"/>
+      <c r="CD102" s="14"/>
       <c r="CE102" s="3"/>
       <c r="CF102" s="3"/>
       <c r="CG102" s="3"/>
@@ -23506,8 +23500,8 @@
       <c r="GU102" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="19.5">
-      <c r="A103" s="11" t="s">
-        <v>336</v>
+      <c r="A103" s="10" t="s">
+        <v>335</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -23589,7 +23583,7 @@
       <c r="CA103" s="3"/>
       <c r="CB103" s="3"/>
       <c r="CC103" s="3"/>
-      <c r="CD103" s="15"/>
+      <c r="CD103" s="14"/>
       <c r="CE103" s="3"/>
       <c r="CF103" s="3"/>
       <c r="CG103" s="3"/>
@@ -23713,8 +23707,8 @@
       <c r="GU103" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="19.5">
-      <c r="A104" s="11" t="s">
-        <v>337</v>
+      <c r="A104" s="10" t="s">
+        <v>336</v>
       </c>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -23796,7 +23790,7 @@
       <c r="CA104" s="3"/>
       <c r="CB104" s="3"/>
       <c r="CC104" s="3"/>
-      <c r="CD104" s="15"/>
+      <c r="CD104" s="14"/>
       <c r="CE104" s="3"/>
       <c r="CF104" s="3"/>
       <c r="CG104" s="3"/>
@@ -23920,8 +23914,8 @@
       <c r="GU104" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="19.5">
-      <c r="A105" s="11" t="s">
-        <v>338</v>
+      <c r="A105" s="10" t="s">
+        <v>337</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -24003,7 +23997,7 @@
       <c r="CA105" s="3"/>
       <c r="CB105" s="3"/>
       <c r="CC105" s="3"/>
-      <c r="CD105" s="15"/>
+      <c r="CD105" s="14"/>
       <c r="CE105" s="3"/>
       <c r="CF105" s="3"/>
       <c r="CG105" s="3"/>
@@ -24127,8 +24121,8 @@
       <c r="GU105" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="19.5">
-      <c r="A106" s="11" t="s">
-        <v>339</v>
+      <c r="A106" s="10" t="s">
+        <v>338</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -24210,7 +24204,7 @@
       <c r="CA106" s="3"/>
       <c r="CB106" s="3"/>
       <c r="CC106" s="3"/>
-      <c r="CD106" s="15"/>
+      <c r="CD106" s="14"/>
       <c r="CE106" s="3"/>
       <c r="CF106" s="3"/>
       <c r="CG106" s="3"/>
@@ -24334,8 +24328,8 @@
       <c r="GU106" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="19.5">
-      <c r="A107" s="11" t="s">
-        <v>340</v>
+      <c r="A107" s="10" t="s">
+        <v>339</v>
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -24417,7 +24411,7 @@
       <c r="CA107" s="3"/>
       <c r="CB107" s="3"/>
       <c r="CC107" s="3"/>
-      <c r="CD107" s="15"/>
+      <c r="CD107" s="14"/>
       <c r="CE107" s="3"/>
       <c r="CF107" s="3"/>
       <c r="CG107" s="3"/>
@@ -24541,8 +24535,8 @@
       <c r="GU107" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="19.5">
-      <c r="A108" s="11" t="s">
-        <v>341</v>
+      <c r="A108" s="10" t="s">
+        <v>340</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -24624,7 +24618,7 @@
       <c r="CA108" s="3"/>
       <c r="CB108" s="3"/>
       <c r="CC108" s="3"/>
-      <c r="CD108" s="15"/>
+      <c r="CD108" s="14"/>
       <c r="CE108" s="3"/>
       <c r="CF108" s="3"/>
       <c r="CG108" s="3"/>
@@ -24748,8 +24742,8 @@
       <c r="GU108" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="19.5">
-      <c r="A109" s="11" t="s">
-        <v>342</v>
+      <c r="A109" s="10" t="s">
+        <v>341</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -24831,7 +24825,7 @@
       <c r="CA109" s="3"/>
       <c r="CB109" s="3"/>
       <c r="CC109" s="3"/>
-      <c r="CD109" s="15"/>
+      <c r="CD109" s="14"/>
       <c r="CE109" s="3"/>
       <c r="CF109" s="3"/>
       <c r="CG109" s="3"/>
@@ -24955,8 +24949,8 @@
       <c r="GU109" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="19.5">
-      <c r="A110" s="11" t="s">
-        <v>343</v>
+      <c r="A110" s="10" t="s">
+        <v>342</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -25038,7 +25032,7 @@
       <c r="CA110" s="3"/>
       <c r="CB110" s="3"/>
       <c r="CC110" s="3"/>
-      <c r="CD110" s="15"/>
+      <c r="CD110" s="14"/>
       <c r="CE110" s="3"/>
       <c r="CF110" s="3"/>
       <c r="CG110" s="3"/>
@@ -25162,8 +25156,8 @@
       <c r="GU110" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="19.5">
-      <c r="A111" s="11" t="s">
-        <v>344</v>
+      <c r="A111" s="10" t="s">
+        <v>343</v>
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -25245,7 +25239,7 @@
       <c r="CA111" s="3"/>
       <c r="CB111" s="3"/>
       <c r="CC111" s="3"/>
-      <c r="CD111" s="15"/>
+      <c r="CD111" s="14"/>
       <c r="CE111" s="3"/>
       <c r="CF111" s="3"/>
       <c r="CG111" s="3"/>
@@ -25369,8 +25363,8 @@
       <c r="GU111" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="19.5">
-      <c r="A112" s="11" t="s">
-        <v>345</v>
+      <c r="A112" s="10" t="s">
+        <v>344</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -25452,7 +25446,7 @@
       <c r="CA112" s="3"/>
       <c r="CB112" s="3"/>
       <c r="CC112" s="3"/>
-      <c r="CD112" s="15"/>
+      <c r="CD112" s="14"/>
       <c r="CE112" s="3"/>
       <c r="CF112" s="3"/>
       <c r="CG112" s="3"/>
@@ -25576,8 +25570,8 @@
       <c r="GU112" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="19.5">
-      <c r="A113" s="11" t="s">
-        <v>346</v>
+      <c r="A113" s="10" t="s">
+        <v>345</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -25659,7 +25653,7 @@
       <c r="CA113" s="3"/>
       <c r="CB113" s="3"/>
       <c r="CC113" s="3"/>
-      <c r="CD113" s="15"/>
+      <c r="CD113" s="14"/>
       <c r="CE113" s="3"/>
       <c r="CF113" s="3"/>
       <c r="CG113" s="3"/>
@@ -25783,8 +25777,8 @@
       <c r="GU113" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="19.5">
-      <c r="A114" s="11" t="s">
-        <v>347</v>
+      <c r="A114" s="10" t="s">
+        <v>346</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -25866,7 +25860,7 @@
       <c r="CA114" s="3"/>
       <c r="CB114" s="3"/>
       <c r="CC114" s="3"/>
-      <c r="CD114" s="15"/>
+      <c r="CD114" s="14"/>
       <c r="CE114" s="3"/>
       <c r="CF114" s="3"/>
       <c r="CG114" s="3"/>
@@ -25990,8 +25984,8 @@
       <c r="GU114" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="19.5">
-      <c r="A115" s="11" t="s">
-        <v>348</v>
+      <c r="A115" s="10" t="s">
+        <v>347</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -26073,7 +26067,7 @@
       <c r="CA115" s="3"/>
       <c r="CB115" s="3"/>
       <c r="CC115" s="3"/>
-      <c r="CD115" s="15"/>
+      <c r="CD115" s="14"/>
       <c r="CE115" s="3"/>
       <c r="CF115" s="3"/>
       <c r="CG115" s="3"/>
@@ -26197,8 +26191,8 @@
       <c r="GU115" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="19.5">
-      <c r="A116" s="11" t="s">
-        <v>349</v>
+      <c r="A116" s="10" t="s">
+        <v>348</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -26280,7 +26274,7 @@
       <c r="CA116" s="3"/>
       <c r="CB116" s="3"/>
       <c r="CC116" s="3"/>
-      <c r="CD116" s="15"/>
+      <c r="CD116" s="14"/>
       <c r="CE116" s="3"/>
       <c r="CF116" s="3"/>
       <c r="CG116" s="3"/>
@@ -26404,8 +26398,8 @@
       <c r="GU116" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="19.5">
-      <c r="A117" s="11" t="s">
-        <v>350</v>
+      <c r="A117" s="10" t="s">
+        <v>349</v>
       </c>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -26487,7 +26481,7 @@
       <c r="CA117" s="3"/>
       <c r="CB117" s="3"/>
       <c r="CC117" s="3"/>
-      <c r="CD117" s="15"/>
+      <c r="CD117" s="14"/>
       <c r="CE117" s="3"/>
       <c r="CF117" s="3"/>
       <c r="CG117" s="3"/>
@@ -26611,8 +26605,8 @@
       <c r="GU117" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="19.5">
-      <c r="A118" s="11" t="s">
-        <v>351</v>
+      <c r="A118" s="10" t="s">
+        <v>350</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -26694,7 +26688,7 @@
       <c r="CA118" s="3"/>
       <c r="CB118" s="3"/>
       <c r="CC118" s="3"/>
-      <c r="CD118" s="15"/>
+      <c r="CD118" s="14"/>
       <c r="CE118" s="3"/>
       <c r="CF118" s="3"/>
       <c r="CG118" s="3"/>
@@ -26818,8 +26812,8 @@
       <c r="GU118" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="19.5">
-      <c r="A119" s="11" t="s">
-        <v>352</v>
+      <c r="A119" s="10" t="s">
+        <v>351</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -26901,7 +26895,7 @@
       <c r="CA119" s="3"/>
       <c r="CB119" s="3"/>
       <c r="CC119" s="3"/>
-      <c r="CD119" s="15"/>
+      <c r="CD119" s="14"/>
       <c r="CE119" s="3"/>
       <c r="CF119" s="3"/>
       <c r="CG119" s="3"/>
@@ -27025,8 +27019,8 @@
       <c r="GU119" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="19.5">
-      <c r="A120" s="11" t="s">
-        <v>353</v>
+      <c r="A120" s="10" t="s">
+        <v>352</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -27108,7 +27102,7 @@
       <c r="CA120" s="3"/>
       <c r="CB120" s="3"/>
       <c r="CC120" s="3"/>
-      <c r="CD120" s="15"/>
+      <c r="CD120" s="14"/>
       <c r="CE120" s="3"/>
       <c r="CF120" s="3"/>
       <c r="CG120" s="3"/>
@@ -27232,8 +27226,8 @@
       <c r="GU120" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="19.5">
-      <c r="A121" s="11" t="s">
-        <v>354</v>
+      <c r="A121" s="10" t="s">
+        <v>353</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -27315,7 +27309,7 @@
       <c r="CA121" s="3"/>
       <c r="CB121" s="3"/>
       <c r="CC121" s="3"/>
-      <c r="CD121" s="15"/>
+      <c r="CD121" s="14"/>
       <c r="CE121" s="3"/>
       <c r="CF121" s="3"/>
       <c r="CG121" s="3"/>
@@ -27439,8 +27433,8 @@
       <c r="GU121" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="19.5">
-      <c r="A122" s="11" t="s">
-        <v>355</v>
+      <c r="A122" s="10" t="s">
+        <v>354</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -27522,7 +27516,7 @@
       <c r="CA122" s="3"/>
       <c r="CB122" s="3"/>
       <c r="CC122" s="3"/>
-      <c r="CD122" s="15"/>
+      <c r="CD122" s="14"/>
       <c r="CE122" s="3"/>
       <c r="CF122" s="3"/>
       <c r="CG122" s="3"/>
@@ -27646,8 +27640,8 @@
       <c r="GU122" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="19.5">
-      <c r="A123" s="11" t="s">
-        <v>356</v>
+      <c r="A123" s="10" t="s">
+        <v>355</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -27729,7 +27723,7 @@
       <c r="CA123" s="3"/>
       <c r="CB123" s="3"/>
       <c r="CC123" s="3"/>
-      <c r="CD123" s="15"/>
+      <c r="CD123" s="14"/>
       <c r="CE123" s="3"/>
       <c r="CF123" s="3"/>
       <c r="CG123" s="3"/>
@@ -27853,8 +27847,8 @@
       <c r="GU123" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="19.5">
-      <c r="A124" s="11" t="s">
-        <v>357</v>
+      <c r="A124" s="10" t="s">
+        <v>356</v>
       </c>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -27936,7 +27930,7 @@
       <c r="CA124" s="3"/>
       <c r="CB124" s="3"/>
       <c r="CC124" s="3"/>
-      <c r="CD124" s="15"/>
+      <c r="CD124" s="14"/>
       <c r="CE124" s="3"/>
       <c r="CF124" s="3"/>
       <c r="CG124" s="3"/>
@@ -28060,8 +28054,8 @@
       <c r="GU124" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="19.5">
-      <c r="A125" s="11" t="s">
-        <v>358</v>
+      <c r="A125" s="10" t="s">
+        <v>357</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -28143,7 +28137,7 @@
       <c r="CA125" s="3"/>
       <c r="CB125" s="3"/>
       <c r="CC125" s="3"/>
-      <c r="CD125" s="15"/>
+      <c r="CD125" s="14"/>
       <c r="CE125" s="3"/>
       <c r="CF125" s="3"/>
       <c r="CG125" s="3"/>
@@ -28267,8 +28261,8 @@
       <c r="GU125" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="19.5">
-      <c r="A126" s="11" t="s">
-        <v>359</v>
+      <c r="A126" s="10" t="s">
+        <v>358</v>
       </c>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -28350,7 +28344,7 @@
       <c r="CA126" s="3"/>
       <c r="CB126" s="3"/>
       <c r="CC126" s="3"/>
-      <c r="CD126" s="15"/>
+      <c r="CD126" s="14"/>
       <c r="CE126" s="3"/>
       <c r="CF126" s="3"/>
       <c r="CG126" s="3"/>
@@ -28474,8 +28468,8 @@
       <c r="GU126" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="19.5">
-      <c r="A127" s="11" t="s">
-        <v>360</v>
+      <c r="A127" s="10" t="s">
+        <v>359</v>
       </c>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -28557,7 +28551,7 @@
       <c r="CA127" s="3"/>
       <c r="CB127" s="3"/>
       <c r="CC127" s="3"/>
-      <c r="CD127" s="15"/>
+      <c r="CD127" s="14"/>
       <c r="CE127" s="3"/>
       <c r="CF127" s="3"/>
       <c r="CG127" s="3"/>
@@ -28681,8 +28675,8 @@
       <c r="GU127" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="19.5">
-      <c r="A128" s="11" t="s">
-        <v>361</v>
+      <c r="A128" s="10" t="s">
+        <v>360</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -28764,7 +28758,7 @@
       <c r="CA128" s="3"/>
       <c r="CB128" s="3"/>
       <c r="CC128" s="3"/>
-      <c r="CD128" s="15"/>
+      <c r="CD128" s="14"/>
       <c r="CE128" s="3"/>
       <c r="CF128" s="3"/>
       <c r="CG128" s="3"/>
@@ -28888,8 +28882,8 @@
       <c r="GU128" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="19.5">
-      <c r="A129" s="11" t="s">
-        <v>362</v>
+      <c r="A129" s="10" t="s">
+        <v>361</v>
       </c>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -28971,7 +28965,7 @@
       <c r="CA129" s="3"/>
       <c r="CB129" s="3"/>
       <c r="CC129" s="3"/>
-      <c r="CD129" s="15"/>
+      <c r="CD129" s="14"/>
       <c r="CE129" s="3"/>
       <c r="CF129" s="3"/>
       <c r="CG129" s="3"/>
@@ -29095,8 +29089,8 @@
       <c r="GU129" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="19.5">
-      <c r="A130" s="11" t="s">
-        <v>363</v>
+      <c r="A130" s="10" t="s">
+        <v>362</v>
       </c>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -29178,7 +29172,7 @@
       <c r="CA130" s="3"/>
       <c r="CB130" s="3"/>
       <c r="CC130" s="3"/>
-      <c r="CD130" s="15"/>
+      <c r="CD130" s="14"/>
       <c r="CE130" s="3"/>
       <c r="CF130" s="3"/>
       <c r="CG130" s="3"/>
@@ -29302,8 +29296,8 @@
       <c r="GU130" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="19.5">
-      <c r="A131" s="11" t="s">
-        <v>364</v>
+      <c r="A131" s="10" t="s">
+        <v>363</v>
       </c>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -29385,7 +29379,7 @@
       <c r="CA131" s="3"/>
       <c r="CB131" s="3"/>
       <c r="CC131" s="3"/>
-      <c r="CD131" s="15"/>
+      <c r="CD131" s="14"/>
       <c r="CE131" s="3"/>
       <c r="CF131" s="3"/>
       <c r="CG131" s="3"/>
@@ -29509,8 +29503,8 @@
       <c r="GU131" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="19.5">
-      <c r="A132" s="11" t="s">
-        <v>365</v>
+      <c r="A132" s="10" t="s">
+        <v>364</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -29592,7 +29586,7 @@
       <c r="CA132" s="3"/>
       <c r="CB132" s="3"/>
       <c r="CC132" s="3"/>
-      <c r="CD132" s="15"/>
+      <c r="CD132" s="14"/>
       <c r="CE132" s="3"/>
       <c r="CF132" s="3"/>
       <c r="CG132" s="3"/>
@@ -29716,8 +29710,8 @@
       <c r="GU132" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="19.5">
-      <c r="A133" s="11" t="s">
-        <v>366</v>
+      <c r="A133" s="10" t="s">
+        <v>365</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -29799,7 +29793,7 @@
       <c r="CA133" s="3"/>
       <c r="CB133" s="3"/>
       <c r="CC133" s="3"/>
-      <c r="CD133" s="15"/>
+      <c r="CD133" s="14"/>
       <c r="CE133" s="3"/>
       <c r="CF133" s="3"/>
       <c r="CG133" s="3"/>
@@ -29923,8 +29917,8 @@
       <c r="GU133" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="19.5">
-      <c r="A134" s="11" t="s">
-        <v>367</v>
+      <c r="A134" s="10" t="s">
+        <v>366</v>
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -30006,7 +30000,7 @@
       <c r="CA134" s="3"/>
       <c r="CB134" s="3"/>
       <c r="CC134" s="3"/>
-      <c r="CD134" s="15"/>
+      <c r="CD134" s="14"/>
       <c r="CE134" s="3"/>
       <c r="CF134" s="3"/>
       <c r="CG134" s="3"/>
@@ -30130,8 +30124,8 @@
       <c r="GU134" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="19.5">
-      <c r="A135" s="11" t="s">
-        <v>368</v>
+      <c r="A135" s="10" t="s">
+        <v>367</v>
       </c>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -30213,7 +30207,7 @@
       <c r="CA135" s="3"/>
       <c r="CB135" s="3"/>
       <c r="CC135" s="3"/>
-      <c r="CD135" s="15"/>
+      <c r="CD135" s="14"/>
       <c r="CE135" s="3"/>
       <c r="CF135" s="3"/>
       <c r="CG135" s="3"/>
@@ -30337,8 +30331,8 @@
       <c r="GU135" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="19.5">
-      <c r="A136" s="11" t="s">
-        <v>369</v>
+      <c r="A136" s="10" t="s">
+        <v>368</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -30420,7 +30414,7 @@
       <c r="CA136" s="3"/>
       <c r="CB136" s="3"/>
       <c r="CC136" s="3"/>
-      <c r="CD136" s="15"/>
+      <c r="CD136" s="14"/>
       <c r="CE136" s="3"/>
       <c r="CF136" s="3"/>
       <c r="CG136" s="3"/>
@@ -30544,8 +30538,8 @@
       <c r="GU136" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="19.5">
-      <c r="A137" s="11" t="s">
-        <v>370</v>
+      <c r="A137" s="10" t="s">
+        <v>369</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -30627,7 +30621,7 @@
       <c r="CA137" s="3"/>
       <c r="CB137" s="3"/>
       <c r="CC137" s="3"/>
-      <c r="CD137" s="15"/>
+      <c r="CD137" s="14"/>
       <c r="CE137" s="3"/>
       <c r="CF137" s="3"/>
       <c r="CG137" s="3"/>
@@ -30751,8 +30745,8 @@
       <c r="GU137" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="19.5">
-      <c r="A138" s="11" t="s">
-        <v>371</v>
+      <c r="A138" s="10" t="s">
+        <v>370</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -30834,7 +30828,7 @@
       <c r="CA138" s="3"/>
       <c r="CB138" s="3"/>
       <c r="CC138" s="3"/>
-      <c r="CD138" s="15"/>
+      <c r="CD138" s="14"/>
       <c r="CE138" s="3"/>
       <c r="CF138" s="3"/>
       <c r="CG138" s="3"/>
@@ -30958,8 +30952,8 @@
       <c r="GU138" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="19.5">
-      <c r="A139" s="11" t="s">
-        <v>372</v>
+      <c r="A139" s="10" t="s">
+        <v>371</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -31041,7 +31035,7 @@
       <c r="CA139" s="3"/>
       <c r="CB139" s="3"/>
       <c r="CC139" s="3"/>
-      <c r="CD139" s="15"/>
+      <c r="CD139" s="14"/>
       <c r="CE139" s="3"/>
       <c r="CF139" s="3"/>
       <c r="CG139" s="3"/>
@@ -31165,8 +31159,8 @@
       <c r="GU139" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="19.5">
-      <c r="A140" s="11" t="s">
-        <v>373</v>
+      <c r="A140" s="10" t="s">
+        <v>372</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -31248,7 +31242,7 @@
       <c r="CA140" s="3"/>
       <c r="CB140" s="3"/>
       <c r="CC140" s="3"/>
-      <c r="CD140" s="15"/>
+      <c r="CD140" s="14"/>
       <c r="CE140" s="3"/>
       <c r="CF140" s="3"/>
       <c r="CG140" s="3"/>
@@ -31372,8 +31366,8 @@
       <c r="GU140" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="19.5">
-      <c r="A141" s="11" t="s">
-        <v>374</v>
+      <c r="A141" s="10" t="s">
+        <v>373</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -31455,7 +31449,7 @@
       <c r="CA141" s="3"/>
       <c r="CB141" s="3"/>
       <c r="CC141" s="3"/>
-      <c r="CD141" s="15"/>
+      <c r="CD141" s="14"/>
       <c r="CE141" s="3"/>
       <c r="CF141" s="3"/>
       <c r="CG141" s="3"/>
@@ -31579,8 +31573,8 @@
       <c r="GU141" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="19.5">
-      <c r="A142" s="11" t="s">
-        <v>375</v>
+      <c r="A142" s="10" t="s">
+        <v>374</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -31662,7 +31656,7 @@
       <c r="CA142" s="3"/>
       <c r="CB142" s="3"/>
       <c r="CC142" s="3"/>
-      <c r="CD142" s="15"/>
+      <c r="CD142" s="14"/>
       <c r="CE142" s="3"/>
       <c r="CF142" s="3"/>
       <c r="CG142" s="3"/>
@@ -31786,8 +31780,8 @@
       <c r="GU142" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="19.5">
-      <c r="A143" s="11" t="s">
-        <v>376</v>
+      <c r="A143" s="10" t="s">
+        <v>375</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -31869,7 +31863,7 @@
       <c r="CA143" s="3"/>
       <c r="CB143" s="3"/>
       <c r="CC143" s="3"/>
-      <c r="CD143" s="15"/>
+      <c r="CD143" s="14"/>
       <c r="CE143" s="3"/>
       <c r="CF143" s="3"/>
       <c r="CG143" s="3"/>
@@ -31993,8 +31987,8 @@
       <c r="GU143" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="19.5">
-      <c r="A144" s="11" t="s">
-        <v>377</v>
+      <c r="A144" s="10" t="s">
+        <v>376</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -32076,7 +32070,7 @@
       <c r="CA144" s="3"/>
       <c r="CB144" s="3"/>
       <c r="CC144" s="3"/>
-      <c r="CD144" s="15"/>
+      <c r="CD144" s="14"/>
       <c r="CE144" s="3"/>
       <c r="CF144" s="3"/>
       <c r="CG144" s="3"/>
@@ -32200,8 +32194,8 @@
       <c r="GU144" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="19.5">
-      <c r="A145" s="11" t="s">
-        <v>378</v>
+      <c r="A145" s="10" t="s">
+        <v>377</v>
       </c>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -32283,7 +32277,7 @@
       <c r="CA145" s="3"/>
       <c r="CB145" s="3"/>
       <c r="CC145" s="3"/>
-      <c r="CD145" s="15"/>
+      <c r="CD145" s="14"/>
       <c r="CE145" s="3"/>
       <c r="CF145" s="3"/>
       <c r="CG145" s="3"/>
@@ -32407,8 +32401,8 @@
       <c r="GU145" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="19.5">
-      <c r="A146" s="11" t="s">
-        <v>379</v>
+      <c r="A146" s="10" t="s">
+        <v>378</v>
       </c>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -32490,7 +32484,7 @@
       <c r="CA146" s="3"/>
       <c r="CB146" s="3"/>
       <c r="CC146" s="3"/>
-      <c r="CD146" s="15"/>
+      <c r="CD146" s="14"/>
       <c r="CE146" s="3"/>
       <c r="CF146" s="3"/>
       <c r="CG146" s="3"/>
@@ -32614,8 +32608,8 @@
       <c r="GU146" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="19.5">
-      <c r="A147" s="11" t="s">
-        <v>380</v>
+      <c r="A147" s="10" t="s">
+        <v>379</v>
       </c>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -32697,7 +32691,7 @@
       <c r="CA147" s="3"/>
       <c r="CB147" s="3"/>
       <c r="CC147" s="3"/>
-      <c r="CD147" s="15"/>
+      <c r="CD147" s="14"/>
       <c r="CE147" s="3"/>
       <c r="CF147" s="3"/>
       <c r="CG147" s="3"/>
@@ -32821,8 +32815,8 @@
       <c r="GU147" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="19.5">
-      <c r="A148" s="11" t="s">
-        <v>381</v>
+      <c r="A148" s="10" t="s">
+        <v>380</v>
       </c>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -32904,7 +32898,7 @@
       <c r="CA148" s="3"/>
       <c r="CB148" s="3"/>
       <c r="CC148" s="3"/>
-      <c r="CD148" s="15"/>
+      <c r="CD148" s="14"/>
       <c r="CE148" s="3"/>
       <c r="CF148" s="3"/>
       <c r="CG148" s="3"/>
@@ -33028,8 +33022,8 @@
       <c r="GU148" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="19.5">
-      <c r="A149" s="11" t="s">
-        <v>382</v>
+      <c r="A149" s="10" t="s">
+        <v>381</v>
       </c>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -33111,7 +33105,7 @@
       <c r="CA149" s="3"/>
       <c r="CB149" s="3"/>
       <c r="CC149" s="3"/>
-      <c r="CD149" s="15"/>
+      <c r="CD149" s="14"/>
       <c r="CE149" s="3"/>
       <c r="CF149" s="3"/>
       <c r="CG149" s="3"/>
@@ -33235,8 +33229,8 @@
       <c r="GU149" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="19.5">
-      <c r="A150" s="11" t="s">
-        <v>383</v>
+      <c r="A150" s="10" t="s">
+        <v>382</v>
       </c>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -33318,7 +33312,7 @@
       <c r="CA150" s="3"/>
       <c r="CB150" s="3"/>
       <c r="CC150" s="3"/>
-      <c r="CD150" s="15"/>
+      <c r="CD150" s="14"/>
       <c r="CE150" s="3"/>
       <c r="CF150" s="3"/>
       <c r="CG150" s="3"/>
@@ -33442,8 +33436,8 @@
       <c r="GU150" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="19.5">
-      <c r="A151" s="11" t="s">
-        <v>384</v>
+      <c r="A151" s="10" t="s">
+        <v>383</v>
       </c>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -33525,7 +33519,7 @@
       <c r="CA151" s="3"/>
       <c r="CB151" s="3"/>
       <c r="CC151" s="3"/>
-      <c r="CD151" s="15"/>
+      <c r="CD151" s="14"/>
       <c r="CE151" s="3"/>
       <c r="CF151" s="3"/>
       <c r="CG151" s="3"/>
@@ -33649,8 +33643,8 @@
       <c r="GU151" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="19.5">
-      <c r="A152" s="11" t="s">
-        <v>385</v>
+      <c r="A152" s="10" t="s">
+        <v>384</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -33732,7 +33726,7 @@
       <c r="CA152" s="3"/>
       <c r="CB152" s="3"/>
       <c r="CC152" s="3"/>
-      <c r="CD152" s="15"/>
+      <c r="CD152" s="14"/>
       <c r="CE152" s="3"/>
       <c r="CF152" s="3"/>
       <c r="CG152" s="3"/>
@@ -33856,8 +33850,8 @@
       <c r="GU152" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="19.5">
-      <c r="A153" s="11" t="s">
-        <v>386</v>
+      <c r="A153" s="10" t="s">
+        <v>385</v>
       </c>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -33939,7 +33933,7 @@
       <c r="CA153" s="3"/>
       <c r="CB153" s="3"/>
       <c r="CC153" s="3"/>
-      <c r="CD153" s="15"/>
+      <c r="CD153" s="14"/>
       <c r="CE153" s="3"/>
       <c r="CF153" s="3"/>
       <c r="CG153" s="3"/>
@@ -34063,8 +34057,8 @@
       <c r="GU153" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="19.5">
-      <c r="A154" s="11" t="s">
-        <v>387</v>
+      <c r="A154" s="10" t="s">
+        <v>386</v>
       </c>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -34146,7 +34140,7 @@
       <c r="CA154" s="3"/>
       <c r="CB154" s="3"/>
       <c r="CC154" s="3"/>
-      <c r="CD154" s="15"/>
+      <c r="CD154" s="14"/>
       <c r="CE154" s="3"/>
       <c r="CF154" s="3"/>
       <c r="CG154" s="3"/>
@@ -34270,8 +34264,8 @@
       <c r="GU154" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="19.5">
-      <c r="A155" s="11" t="s">
-        <v>388</v>
+      <c r="A155" s="10" t="s">
+        <v>387</v>
       </c>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -34353,7 +34347,7 @@
       <c r="CA155" s="3"/>
       <c r="CB155" s="3"/>
       <c r="CC155" s="3"/>
-      <c r="CD155" s="15"/>
+      <c r="CD155" s="14"/>
       <c r="CE155" s="3"/>
       <c r="CF155" s="3"/>
       <c r="CG155" s="3"/>
@@ -34477,8 +34471,8 @@
       <c r="GU155" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="19.5">
-      <c r="A156" s="11" t="s">
-        <v>389</v>
+      <c r="A156" s="10" t="s">
+        <v>388</v>
       </c>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -34560,7 +34554,7 @@
       <c r="CA156" s="3"/>
       <c r="CB156" s="3"/>
       <c r="CC156" s="3"/>
-      <c r="CD156" s="15"/>
+      <c r="CD156" s="14"/>
       <c r="CE156" s="3"/>
       <c r="CF156" s="3"/>
       <c r="CG156" s="3"/>
@@ -34684,8 +34678,8 @@
       <c r="GU156" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="19.5">
-      <c r="A157" s="11" t="s">
-        <v>390</v>
+      <c r="A157" s="10" t="s">
+        <v>389</v>
       </c>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -34767,7 +34761,7 @@
       <c r="CA157" s="3"/>
       <c r="CB157" s="3"/>
       <c r="CC157" s="3"/>
-      <c r="CD157" s="15"/>
+      <c r="CD157" s="14"/>
       <c r="CE157" s="3"/>
       <c r="CF157" s="3"/>
       <c r="CG157" s="3"/>
@@ -34891,8 +34885,8 @@
       <c r="GU157" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="19.5">
-      <c r="A158" s="11" t="s">
-        <v>391</v>
+      <c r="A158" s="10" t="s">
+        <v>390</v>
       </c>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -34974,7 +34968,7 @@
       <c r="CA158" s="3"/>
       <c r="CB158" s="3"/>
       <c r="CC158" s="3"/>
-      <c r="CD158" s="15"/>
+      <c r="CD158" s="14"/>
       <c r="CE158" s="3"/>
       <c r="CF158" s="3"/>
       <c r="CG158" s="3"/>
@@ -35098,8 +35092,8 @@
       <c r="GU158" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="19.5">
-      <c r="A159" s="11" t="s">
-        <v>392</v>
+      <c r="A159" s="10" t="s">
+        <v>391</v>
       </c>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -35181,7 +35175,7 @@
       <c r="CA159" s="3"/>
       <c r="CB159" s="3"/>
       <c r="CC159" s="3"/>
-      <c r="CD159" s="15"/>
+      <c r="CD159" s="14"/>
       <c r="CE159" s="3"/>
       <c r="CF159" s="3"/>
       <c r="CG159" s="3"/>
@@ -35305,8 +35299,8 @@
       <c r="GU159" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="19.5">
-      <c r="A160" s="11" t="s">
-        <v>393</v>
+      <c r="A160" s="10" t="s">
+        <v>392</v>
       </c>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -35388,7 +35382,7 @@
       <c r="CA160" s="3"/>
       <c r="CB160" s="3"/>
       <c r="CC160" s="3"/>
-      <c r="CD160" s="15"/>
+      <c r="CD160" s="14"/>
       <c r="CE160" s="3"/>
       <c r="CF160" s="3"/>
       <c r="CG160" s="3"/>
@@ -35512,8 +35506,8 @@
       <c r="GU160" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="19.5">
-      <c r="A161" s="11" t="s">
-        <v>394</v>
+      <c r="A161" s="10" t="s">
+        <v>393</v>
       </c>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -35595,7 +35589,7 @@
       <c r="CA161" s="3"/>
       <c r="CB161" s="3"/>
       <c r="CC161" s="3"/>
-      <c r="CD161" s="15"/>
+      <c r="CD161" s="14"/>
       <c r="CE161" s="3"/>
       <c r="CF161" s="3"/>
       <c r="CG161" s="3"/>
@@ -35719,8 +35713,8 @@
       <c r="GU161" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="19.5">
-      <c r="A162" s="11" t="s">
-        <v>395</v>
+      <c r="A162" s="10" t="s">
+        <v>394</v>
       </c>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -35802,7 +35796,7 @@
       <c r="CA162" s="3"/>
       <c r="CB162" s="3"/>
       <c r="CC162" s="3"/>
-      <c r="CD162" s="15"/>
+      <c r="CD162" s="14"/>
       <c r="CE162" s="3"/>
       <c r="CF162" s="3"/>
       <c r="CG162" s="3"/>
@@ -35926,8 +35920,8 @@
       <c r="GU162" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="19.5">
-      <c r="A163" s="11" t="s">
-        <v>396</v>
+      <c r="A163" s="10" t="s">
+        <v>395</v>
       </c>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -36009,7 +36003,7 @@
       <c r="CA163" s="3"/>
       <c r="CB163" s="3"/>
       <c r="CC163" s="3"/>
-      <c r="CD163" s="15"/>
+      <c r="CD163" s="14"/>
       <c r="CE163" s="3"/>
       <c r="CF163" s="3"/>
       <c r="CG163" s="3"/>
@@ -36133,8 +36127,8 @@
       <c r="GU163" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="19.5">
-      <c r="A164" s="11" t="s">
-        <v>397</v>
+      <c r="A164" s="10" t="s">
+        <v>396</v>
       </c>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -36216,7 +36210,7 @@
       <c r="CA164" s="3"/>
       <c r="CB164" s="3"/>
       <c r="CC164" s="3"/>
-      <c r="CD164" s="15"/>
+      <c r="CD164" s="14"/>
       <c r="CE164" s="3"/>
       <c r="CF164" s="3"/>
       <c r="CG164" s="3"/>
@@ -36340,8 +36334,8 @@
       <c r="GU164" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="19.5">
-      <c r="A165" s="11" t="s">
-        <v>398</v>
+      <c r="A165" s="10" t="s">
+        <v>397</v>
       </c>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -36423,7 +36417,7 @@
       <c r="CA165" s="3"/>
       <c r="CB165" s="3"/>
       <c r="CC165" s="3"/>
-      <c r="CD165" s="15"/>
+      <c r="CD165" s="14"/>
       <c r="CE165" s="3"/>
       <c r="CF165" s="3"/>
       <c r="CG165" s="3"/>
@@ -36547,8 +36541,8 @@
       <c r="GU165" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="19.5">
-      <c r="A166" s="11" t="s">
-        <v>399</v>
+      <c r="A166" s="10" t="s">
+        <v>398</v>
       </c>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -36630,7 +36624,7 @@
       <c r="CA166" s="3"/>
       <c r="CB166" s="3"/>
       <c r="CC166" s="3"/>
-      <c r="CD166" s="15"/>
+      <c r="CD166" s="14"/>
       <c r="CE166" s="3"/>
       <c r="CF166" s="3"/>
       <c r="CG166" s="3"/>
@@ -36754,8 +36748,8 @@
       <c r="GU166" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="19.5">
-      <c r="A167" s="11" t="s">
-        <v>400</v>
+      <c r="A167" s="10" t="s">
+        <v>399</v>
       </c>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -36837,7 +36831,7 @@
       <c r="CA167" s="3"/>
       <c r="CB167" s="3"/>
       <c r="CC167" s="3"/>
-      <c r="CD167" s="15"/>
+      <c r="CD167" s="14"/>
       <c r="CE167" s="3"/>
       <c r="CF167" s="3"/>
       <c r="CG167" s="3"/>
@@ -36961,8 +36955,8 @@
       <c r="GU167" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="19.5">
-      <c r="A168" s="11" t="s">
-        <v>401</v>
+      <c r="A168" s="10" t="s">
+        <v>400</v>
       </c>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -37044,7 +37038,7 @@
       <c r="CA168" s="3"/>
       <c r="CB168" s="3"/>
       <c r="CC168" s="3"/>
-      <c r="CD168" s="15"/>
+      <c r="CD168" s="14"/>
       <c r="CE168" s="3"/>
       <c r="CF168" s="3"/>
       <c r="CG168" s="3"/>
@@ -37168,8 +37162,8 @@
       <c r="GU168" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="19.5">
-      <c r="A169" s="11" t="s">
-        <v>402</v>
+      <c r="A169" s="10" t="s">
+        <v>401</v>
       </c>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -37251,7 +37245,7 @@
       <c r="CA169" s="3"/>
       <c r="CB169" s="3"/>
       <c r="CC169" s="3"/>
-      <c r="CD169" s="15"/>
+      <c r="CD169" s="14"/>
       <c r="CE169" s="3"/>
       <c r="CF169" s="3"/>
       <c r="CG169" s="3"/>
@@ -37375,8 +37369,8 @@
       <c r="GU169" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="19.5">
-      <c r="A170" s="11" t="s">
-        <v>403</v>
+      <c r="A170" s="10" t="s">
+        <v>402</v>
       </c>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -37458,7 +37452,7 @@
       <c r="CA170" s="3"/>
       <c r="CB170" s="3"/>
       <c r="CC170" s="3"/>
-      <c r="CD170" s="15"/>
+      <c r="CD170" s="14"/>
       <c r="CE170" s="3"/>
       <c r="CF170" s="3"/>
       <c r="CG170" s="3"/>
@@ -37582,8 +37576,8 @@
       <c r="GU170" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="19.5">
-      <c r="A171" s="11" t="s">
-        <v>404</v>
+      <c r="A171" s="10" t="s">
+        <v>403</v>
       </c>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -37665,7 +37659,7 @@
       <c r="CA171" s="3"/>
       <c r="CB171" s="3"/>
       <c r="CC171" s="3"/>
-      <c r="CD171" s="15"/>
+      <c r="CD171" s="14"/>
       <c r="CE171" s="3"/>
       <c r="CF171" s="3"/>
       <c r="CG171" s="3"/>
@@ -37789,8 +37783,8 @@
       <c r="GU171" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="19.5">
-      <c r="A172" s="11" t="s">
-        <v>405</v>
+      <c r="A172" s="10" t="s">
+        <v>404</v>
       </c>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -37872,7 +37866,7 @@
       <c r="CA172" s="3"/>
       <c r="CB172" s="3"/>
       <c r="CC172" s="3"/>
-      <c r="CD172" s="15"/>
+      <c r="CD172" s="14"/>
       <c r="CE172" s="3"/>
       <c r="CF172" s="3"/>
       <c r="CG172" s="3"/>
@@ -37996,8 +37990,8 @@
       <c r="GU172" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="19.5">
-      <c r="A173" s="11" t="s">
-        <v>406</v>
+      <c r="A173" s="10" t="s">
+        <v>405</v>
       </c>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -38079,7 +38073,7 @@
       <c r="CA173" s="3"/>
       <c r="CB173" s="3"/>
       <c r="CC173" s="3"/>
-      <c r="CD173" s="15"/>
+      <c r="CD173" s="14"/>
       <c r="CE173" s="3"/>
       <c r="CF173" s="3"/>
       <c r="CG173" s="3"/>
@@ -38203,8 +38197,8 @@
       <c r="GU173" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="19.5">
-      <c r="A174" s="11" t="s">
-        <v>407</v>
+      <c r="A174" s="10" t="s">
+        <v>406</v>
       </c>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -38286,7 +38280,7 @@
       <c r="CA174" s="3"/>
       <c r="CB174" s="3"/>
       <c r="CC174" s="3"/>
-      <c r="CD174" s="15"/>
+      <c r="CD174" s="14"/>
       <c r="CE174" s="3"/>
       <c r="CF174" s="3"/>
       <c r="CG174" s="3"/>
@@ -38410,8 +38404,8 @@
       <c r="GU174" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="19.5">
-      <c r="A175" s="11" t="s">
-        <v>408</v>
+      <c r="A175" s="10" t="s">
+        <v>407</v>
       </c>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -38493,7 +38487,7 @@
       <c r="CA175" s="3"/>
       <c r="CB175" s="3"/>
       <c r="CC175" s="3"/>
-      <c r="CD175" s="15"/>
+      <c r="CD175" s="14"/>
       <c r="CE175" s="3"/>
       <c r="CF175" s="3"/>
       <c r="CG175" s="3"/>
@@ -38617,8 +38611,8 @@
       <c r="GU175" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="19.5">
-      <c r="A176" s="11" t="s">
-        <v>409</v>
+      <c r="A176" s="10" t="s">
+        <v>408</v>
       </c>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -38700,7 +38694,7 @@
       <c r="CA176" s="3"/>
       <c r="CB176" s="3"/>
       <c r="CC176" s="3"/>
-      <c r="CD176" s="15"/>
+      <c r="CD176" s="14"/>
       <c r="CE176" s="3"/>
       <c r="CF176" s="3"/>
       <c r="CG176" s="3"/>
@@ -38824,8 +38818,8 @@
       <c r="GU176" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="19.5">
-      <c r="A177" s="11" t="s">
-        <v>410</v>
+      <c r="A177" s="10" t="s">
+        <v>409</v>
       </c>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -38907,7 +38901,7 @@
       <c r="CA177" s="3"/>
       <c r="CB177" s="3"/>
       <c r="CC177" s="3"/>
-      <c r="CD177" s="15"/>
+      <c r="CD177" s="14"/>
       <c r="CE177" s="3"/>
       <c r="CF177" s="3"/>
       <c r="CG177" s="3"/>
@@ -39031,8 +39025,8 @@
       <c r="GU177" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="19.5">
-      <c r="A178" s="11" t="s">
-        <v>411</v>
+      <c r="A178" s="10" t="s">
+        <v>410</v>
       </c>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -39114,7 +39108,7 @@
       <c r="CA178" s="3"/>
       <c r="CB178" s="3"/>
       <c r="CC178" s="3"/>
-      <c r="CD178" s="15"/>
+      <c r="CD178" s="14"/>
       <c r="CE178" s="3"/>
       <c r="CF178" s="3"/>
       <c r="CG178" s="3"/>
@@ -39238,8 +39232,8 @@
       <c r="GU178" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="19.5">
-      <c r="A179" s="11" t="s">
-        <v>412</v>
+      <c r="A179" s="10" t="s">
+        <v>411</v>
       </c>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -39321,7 +39315,7 @@
       <c r="CA179" s="3"/>
       <c r="CB179" s="3"/>
       <c r="CC179" s="3"/>
-      <c r="CD179" s="15"/>
+      <c r="CD179" s="14"/>
       <c r="CE179" s="3"/>
       <c r="CF179" s="3"/>
       <c r="CG179" s="3"/>
@@ -39445,8 +39439,8 @@
       <c r="GU179" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="19.5">
-      <c r="A180" s="11" t="s">
-        <v>413</v>
+      <c r="A180" s="10" t="s">
+        <v>412</v>
       </c>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -39528,7 +39522,7 @@
       <c r="CA180" s="3"/>
       <c r="CB180" s="3"/>
       <c r="CC180" s="3"/>
-      <c r="CD180" s="15"/>
+      <c r="CD180" s="14"/>
       <c r="CE180" s="3"/>
       <c r="CF180" s="3"/>
       <c r="CG180" s="3"/>
@@ -39652,8 +39646,8 @@
       <c r="GU180" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="19.5">
-      <c r="A181" s="11" t="s">
-        <v>414</v>
+      <c r="A181" s="10" t="s">
+        <v>413</v>
       </c>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -39735,7 +39729,7 @@
       <c r="CA181" s="3"/>
       <c r="CB181" s="3"/>
       <c r="CC181" s="3"/>
-      <c r="CD181" s="15"/>
+      <c r="CD181" s="14"/>
       <c r="CE181" s="3"/>
       <c r="CF181" s="3"/>
       <c r="CG181" s="3"/>
@@ -39859,8 +39853,8 @@
       <c r="GU181" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="19.5">
-      <c r="A182" s="11" t="s">
-        <v>415</v>
+      <c r="A182" s="10" t="s">
+        <v>414</v>
       </c>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -39942,7 +39936,7 @@
       <c r="CA182" s="3"/>
       <c r="CB182" s="3"/>
       <c r="CC182" s="3"/>
-      <c r="CD182" s="15"/>
+      <c r="CD182" s="14"/>
       <c r="CE182" s="3"/>
       <c r="CF182" s="3"/>
       <c r="CG182" s="3"/>
@@ -40066,8 +40060,8 @@
       <c r="GU182" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="19.5">
-      <c r="A183" s="11" t="s">
-        <v>416</v>
+      <c r="A183" s="10" t="s">
+        <v>415</v>
       </c>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -40149,7 +40143,7 @@
       <c r="CA183" s="3"/>
       <c r="CB183" s="3"/>
       <c r="CC183" s="3"/>
-      <c r="CD183" s="15"/>
+      <c r="CD183" s="14"/>
       <c r="CE183" s="3"/>
       <c r="CF183" s="3"/>
       <c r="CG183" s="3"/>
@@ -40273,8 +40267,8 @@
       <c r="GU183" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="19.5">
-      <c r="A184" s="11" t="s">
-        <v>417</v>
+      <c r="A184" s="10" t="s">
+        <v>416</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -40356,7 +40350,7 @@
       <c r="CA184" s="3"/>
       <c r="CB184" s="3"/>
       <c r="CC184" s="3"/>
-      <c r="CD184" s="15"/>
+      <c r="CD184" s="14"/>
       <c r="CE184" s="3"/>
       <c r="CF184" s="3"/>
       <c r="CG184" s="3"/>
@@ -40480,8 +40474,8 @@
       <c r="GU184" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="19.5">
-      <c r="A185" s="11" t="s">
-        <v>418</v>
+      <c r="A185" s="10" t="s">
+        <v>417</v>
       </c>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -40563,7 +40557,7 @@
       <c r="CA185" s="3"/>
       <c r="CB185" s="3"/>
       <c r="CC185" s="3"/>
-      <c r="CD185" s="15"/>
+      <c r="CD185" s="14"/>
       <c r="CE185" s="3"/>
       <c r="CF185" s="3"/>
       <c r="CG185" s="3"/>
@@ -40687,8 +40681,8 @@
       <c r="GU185" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="19.5">
-      <c r="A186" s="11" t="s">
-        <v>419</v>
+      <c r="A186" s="10" t="s">
+        <v>418</v>
       </c>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -40770,7 +40764,7 @@
       <c r="CA186" s="3"/>
       <c r="CB186" s="3"/>
       <c r="CC186" s="3"/>
-      <c r="CD186" s="15"/>
+      <c r="CD186" s="14"/>
       <c r="CE186" s="3"/>
       <c r="CF186" s="3"/>
       <c r="CG186" s="3"/>
@@ -40894,8 +40888,8 @@
       <c r="GU186" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="19.5">
-      <c r="A187" s="11" t="s">
-        <v>420</v>
+      <c r="A187" s="10" t="s">
+        <v>419</v>
       </c>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -40977,7 +40971,7 @@
       <c r="CA187" s="3"/>
       <c r="CB187" s="3"/>
       <c r="CC187" s="3"/>
-      <c r="CD187" s="15"/>
+      <c r="CD187" s="14"/>
       <c r="CE187" s="3"/>
       <c r="CF187" s="3"/>
       <c r="CG187" s="3"/>
@@ -41101,8 +41095,8 @@
       <c r="GU187" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="19.5">
-      <c r="A188" s="11" t="s">
-        <v>421</v>
+      <c r="A188" s="10" t="s">
+        <v>420</v>
       </c>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -41184,7 +41178,7 @@
       <c r="CA188" s="3"/>
       <c r="CB188" s="3"/>
       <c r="CC188" s="3"/>
-      <c r="CD188" s="15"/>
+      <c r="CD188" s="14"/>
       <c r="CE188" s="3"/>
       <c r="CF188" s="3"/>
       <c r="CG188" s="3"/>
@@ -41308,8 +41302,8 @@
       <c r="GU188" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="19.5">
-      <c r="A189" s="11" t="s">
-        <v>422</v>
+      <c r="A189" s="10" t="s">
+        <v>421</v>
       </c>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -41391,7 +41385,7 @@
       <c r="CA189" s="3"/>
       <c r="CB189" s="3"/>
       <c r="CC189" s="3"/>
-      <c r="CD189" s="15"/>
+      <c r="CD189" s="14"/>
       <c r="CE189" s="3"/>
       <c r="CF189" s="3"/>
       <c r="CG189" s="3"/>
@@ -41515,8 +41509,8 @@
       <c r="GU189" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="19.5">
-      <c r="A190" s="11" t="s">
-        <v>423</v>
+      <c r="A190" s="10" t="s">
+        <v>422</v>
       </c>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -41598,7 +41592,7 @@
       <c r="CA190" s="3"/>
       <c r="CB190" s="3"/>
       <c r="CC190" s="3"/>
-      <c r="CD190" s="15"/>
+      <c r="CD190" s="14"/>
       <c r="CE190" s="3"/>
       <c r="CF190" s="3"/>
       <c r="CG190" s="3"/>
@@ -41722,8 +41716,8 @@
       <c r="GU190" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="19.5">
-      <c r="A191" s="11" t="s">
-        <v>424</v>
+      <c r="A191" s="10" t="s">
+        <v>423</v>
       </c>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -41805,7 +41799,7 @@
       <c r="CA191" s="3"/>
       <c r="CB191" s="3"/>
       <c r="CC191" s="3"/>
-      <c r="CD191" s="15"/>
+      <c r="CD191" s="14"/>
       <c r="CE191" s="3"/>
       <c r="CF191" s="3"/>
       <c r="CG191" s="3"/>
@@ -41929,8 +41923,8 @@
       <c r="GU191" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="19.5">
-      <c r="A192" s="11" t="s">
-        <v>425</v>
+      <c r="A192" s="10" t="s">
+        <v>424</v>
       </c>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -42012,7 +42006,7 @@
       <c r="CA192" s="3"/>
       <c r="CB192" s="3"/>
       <c r="CC192" s="3"/>
-      <c r="CD192" s="15"/>
+      <c r="CD192" s="14"/>
       <c r="CE192" s="3"/>
       <c r="CF192" s="3"/>
       <c r="CG192" s="3"/>
@@ -42136,8 +42130,8 @@
       <c r="GU192" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="19.5">
-      <c r="A193" s="11" t="s">
-        <v>426</v>
+      <c r="A193" s="10" t="s">
+        <v>425</v>
       </c>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -42219,7 +42213,7 @@
       <c r="CA193" s="3"/>
       <c r="CB193" s="3"/>
       <c r="CC193" s="3"/>
-      <c r="CD193" s="15"/>
+      <c r="CD193" s="14"/>
       <c r="CE193" s="3"/>
       <c r="CF193" s="3"/>
       <c r="CG193" s="3"/>
@@ -42343,8 +42337,8 @@
       <c r="GU193" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="19.5">
-      <c r="A194" s="11" t="s">
-        <v>427</v>
+      <c r="A194" s="10" t="s">
+        <v>426</v>
       </c>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -42426,7 +42420,7 @@
       <c r="CA194" s="3"/>
       <c r="CB194" s="3"/>
       <c r="CC194" s="3"/>
-      <c r="CD194" s="15"/>
+      <c r="CD194" s="14"/>
       <c r="CE194" s="3"/>
       <c r="CF194" s="3"/>
       <c r="CG194" s="3"/>
@@ -42550,8 +42544,8 @@
       <c r="GU194" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="19.5">
-      <c r="A195" s="11" t="s">
-        <v>428</v>
+      <c r="A195" s="10" t="s">
+        <v>427</v>
       </c>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -42633,7 +42627,7 @@
       <c r="CA195" s="3"/>
       <c r="CB195" s="3"/>
       <c r="CC195" s="3"/>
-      <c r="CD195" s="15"/>
+      <c r="CD195" s="14"/>
       <c r="CE195" s="3"/>
       <c r="CF195" s="3"/>
       <c r="CG195" s="3"/>
@@ -42757,8 +42751,8 @@
       <c r="GU195" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="19.5">
-      <c r="A196" s="11" t="s">
-        <v>429</v>
+      <c r="A196" s="10" t="s">
+        <v>428</v>
       </c>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -42840,7 +42834,7 @@
       <c r="CA196" s="3"/>
       <c r="CB196" s="3"/>
       <c r="CC196" s="3"/>
-      <c r="CD196" s="15"/>
+      <c r="CD196" s="14"/>
       <c r="CE196" s="3"/>
       <c r="CF196" s="3"/>
       <c r="CG196" s="3"/>
@@ -42964,8 +42958,8 @@
       <c r="GU196" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="19.5">
-      <c r="A197" s="11" t="s">
-        <v>430</v>
+      <c r="A197" s="10" t="s">
+        <v>429</v>
       </c>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -43047,7 +43041,7 @@
       <c r="CA197" s="3"/>
       <c r="CB197" s="3"/>
       <c r="CC197" s="3"/>
-      <c r="CD197" s="15"/>
+      <c r="CD197" s="14"/>
       <c r="CE197" s="3"/>
       <c r="CF197" s="3"/>
       <c r="CG197" s="3"/>
@@ -43171,8 +43165,8 @@
       <c r="GU197" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="19.5">
-      <c r="A198" s="11" t="s">
-        <v>431</v>
+      <c r="A198" s="10" t="s">
+        <v>430</v>
       </c>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -43254,7 +43248,7 @@
       <c r="CA198" s="3"/>
       <c r="CB198" s="3"/>
       <c r="CC198" s="3"/>
-      <c r="CD198" s="15"/>
+      <c r="CD198" s="14"/>
       <c r="CE198" s="3"/>
       <c r="CF198" s="3"/>
       <c r="CG198" s="3"/>
@@ -43378,8 +43372,8 @@
       <c r="GU198" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="19.5">
-      <c r="A199" s="11" t="s">
-        <v>432</v>
+      <c r="A199" s="10" t="s">
+        <v>431</v>
       </c>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -43461,7 +43455,7 @@
       <c r="CA199" s="3"/>
       <c r="CB199" s="3"/>
       <c r="CC199" s="3"/>
-      <c r="CD199" s="15"/>
+      <c r="CD199" s="14"/>
       <c r="CE199" s="3"/>
       <c r="CF199" s="3"/>
       <c r="CG199" s="3"/>
@@ -43585,8 +43579,8 @@
       <c r="GU199" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="19.5">
-      <c r="A200" s="11" t="s">
-        <v>433</v>
+      <c r="A200" s="10" t="s">
+        <v>432</v>
       </c>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -43668,7 +43662,7 @@
       <c r="CA200" s="3"/>
       <c r="CB200" s="3"/>
       <c r="CC200" s="3"/>
-      <c r="CD200" s="15"/>
+      <c r="CD200" s="14"/>
       <c r="CE200" s="3"/>
       <c r="CF200" s="3"/>
       <c r="CG200" s="3"/>
@@ -43792,8 +43786,8 @@
       <c r="GU200" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="19.5">
-      <c r="A201" s="11" t="s">
-        <v>434</v>
+      <c r="A201" s="10" t="s">
+        <v>433</v>
       </c>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -43875,7 +43869,7 @@
       <c r="CA201" s="3"/>
       <c r="CB201" s="3"/>
       <c r="CC201" s="3"/>
-      <c r="CD201" s="15"/>
+      <c r="CD201" s="14"/>
       <c r="CE201" s="3"/>
       <c r="CF201" s="3"/>
       <c r="CG201" s="3"/>
@@ -43999,8 +43993,8 @@
       <c r="GU201" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="19.5">
-      <c r="A202" s="11" t="s">
-        <v>435</v>
+      <c r="A202" s="10" t="s">
+        <v>434</v>
       </c>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -44082,7 +44076,7 @@
       <c r="CA202" s="3"/>
       <c r="CB202" s="3"/>
       <c r="CC202" s="3"/>
-      <c r="CD202" s="15"/>
+      <c r="CD202" s="14"/>
       <c r="CE202" s="3"/>
       <c r="CF202" s="3"/>
       <c r="CG202" s="3"/>
@@ -44206,7 +44200,7 @@
       <c r="GU202" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="19.5">
-      <c r="A203" s="11"/>
+      <c r="A203" s="10"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
@@ -44287,7 +44281,7 @@
       <c r="CA203" s="3"/>
       <c r="CB203" s="3"/>
       <c r="CC203" s="3"/>
-      <c r="CD203" s="15"/>
+      <c r="CD203" s="14"/>
       <c r="CE203" s="3"/>
       <c r="CF203" s="3"/>
       <c r="CG203" s="3"/>
@@ -44411,7 +44405,7 @@
       <c r="GU203" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="19.5">
-      <c r="A204" s="11"/>
+      <c r="A204" s="10"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
@@ -44492,7 +44486,7 @@
       <c r="CA204" s="3"/>
       <c r="CB204" s="3"/>
       <c r="CC204" s="3"/>
-      <c r="CD204" s="15"/>
+      <c r="CD204" s="14"/>
       <c r="CE204" s="3"/>
       <c r="CF204" s="3"/>
       <c r="CG204" s="3"/>
@@ -44616,7 +44610,7 @@
       <c r="GU204" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="19.5">
-      <c r="A205" s="11"/>
+      <c r="A205" s="10"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
@@ -44697,7 +44691,7 @@
       <c r="CA205" s="3"/>
       <c r="CB205" s="3"/>
       <c r="CC205" s="3"/>
-      <c r="CD205" s="15"/>
+      <c r="CD205" s="14"/>
       <c r="CE205" s="3"/>
       <c r="CF205" s="3"/>
       <c r="CG205" s="3"/>
@@ -44821,7 +44815,7 @@
       <c r="GU205" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="19.5">
-      <c r="A206" s="11"/>
+      <c r="A206" s="10"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
@@ -44902,7 +44896,7 @@
       <c r="CA206" s="3"/>
       <c r="CB206" s="3"/>
       <c r="CC206" s="3"/>
-      <c r="CD206" s="15"/>
+      <c r="CD206" s="14"/>
       <c r="CE206" s="3"/>
       <c r="CF206" s="3"/>
       <c r="CG206" s="3"/>
@@ -45026,7 +45020,7 @@
       <c r="GU206" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="19.5">
-      <c r="A207" s="11"/>
+      <c r="A207" s="10"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
@@ -45107,7 +45101,7 @@
       <c r="CA207" s="3"/>
       <c r="CB207" s="3"/>
       <c r="CC207" s="3"/>
-      <c r="CD207" s="15"/>
+      <c r="CD207" s="14"/>
       <c r="CE207" s="3"/>
       <c r="CF207" s="3"/>
       <c r="CG207" s="3"/>
@@ -45231,7 +45225,7 @@
       <c r="GU207" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="19.5">
-      <c r="A208" s="11"/>
+      <c r="A208" s="10"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
@@ -45312,7 +45306,7 @@
       <c r="CA208" s="3"/>
       <c r="CB208" s="3"/>
       <c r="CC208" s="3"/>
-      <c r="CD208" s="15"/>
+      <c r="CD208" s="14"/>
       <c r="CE208" s="3"/>
       <c r="CF208" s="3"/>
       <c r="CG208" s="3"/>
@@ -45436,7 +45430,7 @@
       <c r="GU208" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="19.5">
-      <c r="A209" s="11"/>
+      <c r="A209" s="10"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
@@ -45517,7 +45511,7 @@
       <c r="CA209" s="3"/>
       <c r="CB209" s="3"/>
       <c r="CC209" s="3"/>
-      <c r="CD209" s="15"/>
+      <c r="CD209" s="14"/>
       <c r="CE209" s="3"/>
       <c r="CF209" s="3"/>
       <c r="CG209" s="3"/>
@@ -45641,7 +45635,7 @@
       <c r="GU209" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="19.5">
-      <c r="A210" s="11"/>
+      <c r="A210" s="10"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
@@ -45722,7 +45716,7 @@
       <c r="CA210" s="3"/>
       <c r="CB210" s="3"/>
       <c r="CC210" s="3"/>
-      <c r="CD210" s="15"/>
+      <c r="CD210" s="14"/>
       <c r="CE210" s="3"/>
       <c r="CF210" s="3"/>
       <c r="CG210" s="3"/>
@@ -45846,7 +45840,7 @@
       <c r="GU210" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="19.5">
-      <c r="A211" s="11"/>
+      <c r="A211" s="10"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
@@ -45927,7 +45921,7 @@
       <c r="CA211" s="3"/>
       <c r="CB211" s="3"/>
       <c r="CC211" s="3"/>
-      <c r="CD211" s="15"/>
+      <c r="CD211" s="14"/>
       <c r="CE211" s="3"/>
       <c r="CF211" s="3"/>
       <c r="CG211" s="3"/>
@@ -46051,7 +46045,7 @@
       <c r="GU211" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="19.5">
-      <c r="A212" s="11"/>
+      <c r="A212" s="10"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
@@ -46132,7 +46126,7 @@
       <c r="CA212" s="3"/>
       <c r="CB212" s="3"/>
       <c r="CC212" s="3"/>
-      <c r="CD212" s="15"/>
+      <c r="CD212" s="14"/>
       <c r="CE212" s="3"/>
       <c r="CF212" s="3"/>
       <c r="CG212" s="3"/>
@@ -46256,7 +46250,7 @@
       <c r="GU212" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="19.5">
-      <c r="A213" s="11"/>
+      <c r="A213" s="10"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
@@ -46337,7 +46331,7 @@
       <c r="CA213" s="3"/>
       <c r="CB213" s="3"/>
       <c r="CC213" s="3"/>
-      <c r="CD213" s="15"/>
+      <c r="CD213" s="14"/>
       <c r="CE213" s="3"/>
       <c r="CF213" s="3"/>
       <c r="CG213" s="3"/>
@@ -46461,7 +46455,7 @@
       <c r="GU213" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="19.5">
-      <c r="A214" s="11"/>
+      <c r="A214" s="10"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
@@ -46542,7 +46536,7 @@
       <c r="CA214" s="3"/>
       <c r="CB214" s="3"/>
       <c r="CC214" s="3"/>
-      <c r="CD214" s="15"/>
+      <c r="CD214" s="14"/>
       <c r="CE214" s="3"/>
       <c r="CF214" s="3"/>
       <c r="CG214" s="3"/>
@@ -46666,7 +46660,7 @@
       <c r="GU214" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="19.5">
-      <c r="A215" s="11"/>
+      <c r="A215" s="10"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
@@ -46747,7 +46741,7 @@
       <c r="CA215" s="3"/>
       <c r="CB215" s="3"/>
       <c r="CC215" s="3"/>
-      <c r="CD215" s="15"/>
+      <c r="CD215" s="14"/>
       <c r="CE215" s="3"/>
       <c r="CF215" s="3"/>
       <c r="CG215" s="3"/>
@@ -46871,7 +46865,7 @@
       <c r="GU215" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="19.5">
-      <c r="A216" s="11"/>
+      <c r="A216" s="10"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
@@ -46952,7 +46946,7 @@
       <c r="CA216" s="3"/>
       <c r="CB216" s="3"/>
       <c r="CC216" s="3"/>
-      <c r="CD216" s="15"/>
+      <c r="CD216" s="14"/>
       <c r="CE216" s="3"/>
       <c r="CF216" s="3"/>
       <c r="CG216" s="3"/>
@@ -47076,7 +47070,7 @@
       <c r="GU216" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="19.5">
-      <c r="A217" s="11"/>
+      <c r="A217" s="10"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
@@ -47157,7 +47151,7 @@
       <c r="CA217" s="3"/>
       <c r="CB217" s="3"/>
       <c r="CC217" s="3"/>
-      <c r="CD217" s="15"/>
+      <c r="CD217" s="14"/>
       <c r="CE217" s="3"/>
       <c r="CF217" s="3"/>
       <c r="CG217" s="3"/>
@@ -47281,7 +47275,7 @@
       <c r="GU217" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="19.5">
-      <c r="A218" s="11"/>
+      <c r="A218" s="10"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
@@ -47362,7 +47356,7 @@
       <c r="CA218" s="3"/>
       <c r="CB218" s="3"/>
       <c r="CC218" s="3"/>
-      <c r="CD218" s="15"/>
+      <c r="CD218" s="14"/>
       <c r="CE218" s="3"/>
       <c r="CF218" s="3"/>
       <c r="CG218" s="3"/>
@@ -47486,7 +47480,7 @@
       <c r="GU218" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="19.5">
-      <c r="A219" s="11"/>
+      <c r="A219" s="10"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
@@ -47567,7 +47561,7 @@
       <c r="CA219" s="3"/>
       <c r="CB219" s="3"/>
       <c r="CC219" s="3"/>
-      <c r="CD219" s="15"/>
+      <c r="CD219" s="14"/>
       <c r="CE219" s="3"/>
       <c r="CF219" s="3"/>
       <c r="CG219" s="3"/>
@@ -47691,7 +47685,7 @@
       <c r="GU219" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="19.5">
-      <c r="A220" s="11"/>
+      <c r="A220" s="10"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
@@ -47772,7 +47766,7 @@
       <c r="CA220" s="3"/>
       <c r="CB220" s="3"/>
       <c r="CC220" s="3"/>
-      <c r="CD220" s="15"/>
+      <c r="CD220" s="14"/>
       <c r="CE220" s="3"/>
       <c r="CF220" s="3"/>
       <c r="CG220" s="3"/>
@@ -47896,7 +47890,7 @@
       <c r="GU220" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="19.5">
-      <c r="A221" s="11"/>
+      <c r="A221" s="10"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
@@ -47977,7 +47971,7 @@
       <c r="CA221" s="3"/>
       <c r="CB221" s="3"/>
       <c r="CC221" s="3"/>
-      <c r="CD221" s="15"/>
+      <c r="CD221" s="14"/>
       <c r="CE221" s="3"/>
       <c r="CF221" s="3"/>
       <c r="CG221" s="3"/>
@@ -48101,7 +48095,7 @@
       <c r="GU221" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="19.5">
-      <c r="A222" s="11"/>
+      <c r="A222" s="10"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
@@ -48182,7 +48176,7 @@
       <c r="CA222" s="3"/>
       <c r="CB222" s="3"/>
       <c r="CC222" s="3"/>
-      <c r="CD222" s="15"/>
+      <c r="CD222" s="14"/>
       <c r="CE222" s="3"/>
       <c r="CF222" s="3"/>
       <c r="CG222" s="3"/>
@@ -48306,7 +48300,7 @@
       <c r="GU222" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="19.5">
-      <c r="A223" s="11"/>
+      <c r="A223" s="10"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
@@ -48387,7 +48381,7 @@
       <c r="CA223" s="3"/>
       <c r="CB223" s="3"/>
       <c r="CC223" s="3"/>
-      <c r="CD223" s="15"/>
+      <c r="CD223" s="14"/>
       <c r="CE223" s="3"/>
       <c r="CF223" s="3"/>
       <c r="CG223" s="3"/>
@@ -48511,7 +48505,7 @@
       <c r="GU223" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="19.5">
-      <c r="A224" s="11"/>
+      <c r="A224" s="10"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
@@ -48592,7 +48586,7 @@
       <c r="CA224" s="3"/>
       <c r="CB224" s="3"/>
       <c r="CC224" s="3"/>
-      <c r="CD224" s="15"/>
+      <c r="CD224" s="14"/>
       <c r="CE224" s="3"/>
       <c r="CF224" s="3"/>
       <c r="CG224" s="3"/>
@@ -48716,7 +48710,7 @@
       <c r="GU224" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="19.5">
-      <c r="A225" s="11"/>
+      <c r="A225" s="10"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
@@ -48797,7 +48791,7 @@
       <c r="CA225" s="3"/>
       <c r="CB225" s="3"/>
       <c r="CC225" s="3"/>
-      <c r="CD225" s="15"/>
+      <c r="CD225" s="14"/>
       <c r="CE225" s="3"/>
       <c r="CF225" s="3"/>
       <c r="CG225" s="3"/>
@@ -48921,7 +48915,7 @@
       <c r="GU225" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="19.5">
-      <c r="A226" s="11"/>
+      <c r="A226" s="10"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
@@ -49002,7 +48996,7 @@
       <c r="CA226" s="3"/>
       <c r="CB226" s="3"/>
       <c r="CC226" s="3"/>
-      <c r="CD226" s="15"/>
+      <c r="CD226" s="14"/>
       <c r="CE226" s="3"/>
       <c r="CF226" s="3"/>
       <c r="CG226" s="3"/>
@@ -49126,7 +49120,7 @@
       <c r="GU226" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="19.5">
-      <c r="A227" s="11"/>
+      <c r="A227" s="10"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
@@ -49207,7 +49201,7 @@
       <c r="CA227" s="3"/>
       <c r="CB227" s="3"/>
       <c r="CC227" s="3"/>
-      <c r="CD227" s="15"/>
+      <c r="CD227" s="14"/>
       <c r="CE227" s="3"/>
       <c r="CF227" s="3"/>
       <c r="CG227" s="3"/>
@@ -49331,7 +49325,7 @@
       <c r="GU227" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="19.5">
-      <c r="A228" s="11"/>
+      <c r="A228" s="10"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
@@ -49412,7 +49406,7 @@
       <c r="CA228" s="3"/>
       <c r="CB228" s="3"/>
       <c r="CC228" s="3"/>
-      <c r="CD228" s="15"/>
+      <c r="CD228" s="14"/>
       <c r="CE228" s="3"/>
       <c r="CF228" s="3"/>
       <c r="CG228" s="3"/>
@@ -49536,7 +49530,7 @@
       <c r="GU228" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="19.5">
-      <c r="A229" s="11"/>
+      <c r="A229" s="10"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
@@ -49617,7 +49611,7 @@
       <c r="CA229" s="3"/>
       <c r="CB229" s="3"/>
       <c r="CC229" s="3"/>
-      <c r="CD229" s="15"/>
+      <c r="CD229" s="14"/>
       <c r="CE229" s="3"/>
       <c r="CF229" s="3"/>
       <c r="CG229" s="3"/>
@@ -49741,7 +49735,7 @@
       <c r="GU229" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="19.5">
-      <c r="A230" s="11"/>
+      <c r="A230" s="10"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
@@ -49822,7 +49816,7 @@
       <c r="CA230" s="3"/>
       <c r="CB230" s="3"/>
       <c r="CC230" s="3"/>
-      <c r="CD230" s="15"/>
+      <c r="CD230" s="14"/>
       <c r="CE230" s="3"/>
       <c r="CF230" s="3"/>
       <c r="CG230" s="3"/>
@@ -49946,7 +49940,7 @@
       <c r="GU230" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="19.5">
-      <c r="A231" s="11"/>
+      <c r="A231" s="10"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
@@ -50027,7 +50021,7 @@
       <c r="CA231" s="3"/>
       <c r="CB231" s="3"/>
       <c r="CC231" s="3"/>
-      <c r="CD231" s="15"/>
+      <c r="CD231" s="14"/>
       <c r="CE231" s="3"/>
       <c r="CF231" s="3"/>
       <c r="CG231" s="3"/>
@@ -50151,7 +50145,7 @@
       <c r="GU231" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="19.5">
-      <c r="A232" s="11"/>
+      <c r="A232" s="10"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
@@ -50232,7 +50226,7 @@
       <c r="CA232" s="3"/>
       <c r="CB232" s="3"/>
       <c r="CC232" s="3"/>
-      <c r="CD232" s="15"/>
+      <c r="CD232" s="14"/>
       <c r="CE232" s="3"/>
       <c r="CF232" s="3"/>
       <c r="CG232" s="3"/>
@@ -50356,7 +50350,7 @@
       <c r="GU232" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="19.5">
-      <c r="A233" s="11"/>
+      <c r="A233" s="10"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
@@ -50437,7 +50431,7 @@
       <c r="CA233" s="3"/>
       <c r="CB233" s="3"/>
       <c r="CC233" s="3"/>
-      <c r="CD233" s="15"/>
+      <c r="CD233" s="14"/>
       <c r="CE233" s="3"/>
       <c r="CF233" s="3"/>
       <c r="CG233" s="3"/>
@@ -50561,7 +50555,7 @@
       <c r="GU233" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="19.5">
-      <c r="A234" s="11"/>
+      <c r="A234" s="10"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
@@ -50642,7 +50636,7 @@
       <c r="CA234" s="3"/>
       <c r="CB234" s="3"/>
       <c r="CC234" s="3"/>
-      <c r="CD234" s="15"/>
+      <c r="CD234" s="14"/>
       <c r="CE234" s="3"/>
       <c r="CF234" s="3"/>
       <c r="CG234" s="3"/>
@@ -50766,7 +50760,7 @@
       <c r="GU234" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="19.5">
-      <c r="A235" s="11"/>
+      <c r="A235" s="10"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
@@ -50847,7 +50841,7 @@
       <c r="CA235" s="3"/>
       <c r="CB235" s="3"/>
       <c r="CC235" s="3"/>
-      <c r="CD235" s="15"/>
+      <c r="CD235" s="14"/>
       <c r="CE235" s="3"/>
       <c r="CF235" s="3"/>
       <c r="CG235" s="3"/>
@@ -50971,7 +50965,7 @@
       <c r="GU235" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="19.5">
-      <c r="A236" s="11"/>
+      <c r="A236" s="10"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
@@ -51052,7 +51046,7 @@
       <c r="CA236" s="3"/>
       <c r="CB236" s="3"/>
       <c r="CC236" s="3"/>
-      <c r="CD236" s="15"/>
+      <c r="CD236" s="14"/>
       <c r="CE236" s="3"/>
       <c r="CF236" s="3"/>
       <c r="CG236" s="3"/>
@@ -51176,7 +51170,7 @@
       <c r="GU236" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="19.5">
-      <c r="A237" s="11"/>
+      <c r="A237" s="10"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
@@ -51257,7 +51251,7 @@
       <c r="CA237" s="3"/>
       <c r="CB237" s="3"/>
       <c r="CC237" s="3"/>
-      <c r="CD237" s="15"/>
+      <c r="CD237" s="14"/>
       <c r="CE237" s="3"/>
       <c r="CF237" s="3"/>
       <c r="CG237" s="3"/>
@@ -51381,7 +51375,7 @@
       <c r="GU237" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="19.5">
-      <c r="A238" s="11"/>
+      <c r="A238" s="10"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
@@ -51462,7 +51456,7 @@
       <c r="CA238" s="3"/>
       <c r="CB238" s="3"/>
       <c r="CC238" s="3"/>
-      <c r="CD238" s="15"/>
+      <c r="CD238" s="14"/>
       <c r="CE238" s="3"/>
       <c r="CF238" s="3"/>
       <c r="CG238" s="3"/>
@@ -51586,7 +51580,7 @@
       <c r="GU238" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="19.5">
-      <c r="A239" s="11"/>
+      <c r="A239" s="10"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
@@ -51667,7 +51661,7 @@
       <c r="CA239" s="3"/>
       <c r="CB239" s="3"/>
       <c r="CC239" s="3"/>
-      <c r="CD239" s="15"/>
+      <c r="CD239" s="14"/>
       <c r="CE239" s="3"/>
       <c r="CF239" s="3"/>
       <c r="CG239" s="3"/>
@@ -51791,7 +51785,7 @@
       <c r="GU239" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="19.5">
-      <c r="A240" s="11"/>
+      <c r="A240" s="10"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
@@ -51872,7 +51866,7 @@
       <c r="CA240" s="3"/>
       <c r="CB240" s="3"/>
       <c r="CC240" s="3"/>
-      <c r="CD240" s="15"/>
+      <c r="CD240" s="14"/>
       <c r="CE240" s="3"/>
       <c r="CF240" s="3"/>
       <c r="CG240" s="3"/>
@@ -51996,7 +51990,7 @@
       <c r="GU240" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="19.5">
-      <c r="A241" s="11"/>
+      <c r="A241" s="10"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
@@ -52077,7 +52071,7 @@
       <c r="CA241" s="3"/>
       <c r="CB241" s="3"/>
       <c r="CC241" s="3"/>
-      <c r="CD241" s="15"/>
+      <c r="CD241" s="14"/>
       <c r="CE241" s="3"/>
       <c r="CF241" s="3"/>
       <c r="CG241" s="3"/>
@@ -52201,7 +52195,7 @@
       <c r="GU241" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="19.5">
-      <c r="A242" s="11"/>
+      <c r="A242" s="10"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
@@ -52282,7 +52276,7 @@
       <c r="CA242" s="3"/>
       <c r="CB242" s="3"/>
       <c r="CC242" s="3"/>
-      <c r="CD242" s="15"/>
+      <c r="CD242" s="14"/>
       <c r="CE242" s="3"/>
       <c r="CF242" s="3"/>
       <c r="CG242" s="3"/>
@@ -52406,7 +52400,7 @@
       <c r="GU242" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="19.5">
-      <c r="A243" s="11"/>
+      <c r="A243" s="10"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
@@ -52487,7 +52481,7 @@
       <c r="CA243" s="3"/>
       <c r="CB243" s="3"/>
       <c r="CC243" s="3"/>
-      <c r="CD243" s="15"/>
+      <c r="CD243" s="14"/>
       <c r="CE243" s="3"/>
       <c r="CF243" s="3"/>
       <c r="CG243" s="3"/>
@@ -52611,7 +52605,7 @@
       <c r="GU243" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="19.5">
-      <c r="A244" s="11"/>
+      <c r="A244" s="10"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
@@ -52692,7 +52686,7 @@
       <c r="CA244" s="3"/>
       <c r="CB244" s="3"/>
       <c r="CC244" s="3"/>
-      <c r="CD244" s="15"/>
+      <c r="CD244" s="14"/>
       <c r="CE244" s="3"/>
       <c r="CF244" s="3"/>
       <c r="CG244" s="3"/>
@@ -52816,7 +52810,7 @@
       <c r="GU244" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="19.5">
-      <c r="A245" s="11"/>
+      <c r="A245" s="10"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
@@ -52897,7 +52891,7 @@
       <c r="CA245" s="3"/>
       <c r="CB245" s="3"/>
       <c r="CC245" s="3"/>
-      <c r="CD245" s="15"/>
+      <c r="CD245" s="14"/>
       <c r="CE245" s="3"/>
       <c r="CF245" s="3"/>
       <c r="CG245" s="3"/>
@@ -53021,7 +53015,7 @@
       <c r="GU245" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="19.5">
-      <c r="A246" s="11"/>
+      <c r="A246" s="10"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
@@ -53102,7 +53096,7 @@
       <c r="CA246" s="3"/>
       <c r="CB246" s="3"/>
       <c r="CC246" s="3"/>
-      <c r="CD246" s="15"/>
+      <c r="CD246" s="14"/>
       <c r="CE246" s="3"/>
       <c r="CF246" s="3"/>
       <c r="CG246" s="3"/>
@@ -53226,7 +53220,7 @@
       <c r="GU246" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="19.5">
-      <c r="A247" s="11"/>
+      <c r="A247" s="10"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
@@ -53307,7 +53301,7 @@
       <c r="CA247" s="3"/>
       <c r="CB247" s="3"/>
       <c r="CC247" s="3"/>
-      <c r="CD247" s="15"/>
+      <c r="CD247" s="14"/>
       <c r="CE247" s="3"/>
       <c r="CF247" s="3"/>
       <c r="CG247" s="3"/>
@@ -53431,7 +53425,7 @@
       <c r="GU247" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="19.5">
-      <c r="A248" s="11"/>
+      <c r="A248" s="10"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
@@ -53512,7 +53506,7 @@
       <c r="CA248" s="3"/>
       <c r="CB248" s="3"/>
       <c r="CC248" s="3"/>
-      <c r="CD248" s="15"/>
+      <c r="CD248" s="14"/>
       <c r="CE248" s="3"/>
       <c r="CF248" s="3"/>
       <c r="CG248" s="3"/>
@@ -53636,7 +53630,7 @@
       <c r="GU248" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="19.5">
-      <c r="A249" s="11"/>
+      <c r="A249" s="10"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
@@ -53717,7 +53711,7 @@
       <c r="CA249" s="3"/>
       <c r="CB249" s="3"/>
       <c r="CC249" s="3"/>
-      <c r="CD249" s="15"/>
+      <c r="CD249" s="14"/>
       <c r="CE249" s="3"/>
       <c r="CF249" s="3"/>
       <c r="CG249" s="3"/>
@@ -53853,27 +53847,27 @@
   <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="19" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="19" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="20" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="19" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="19" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="19" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="20" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="19" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="19" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="19" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -53919,41 +53913,39 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
-      <c r="E2" s="9" t="s">
-        <v>11</v>
-      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="3"/>
       <c r="K2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="9">
+        <v>165</v>
+      </c>
+      <c r="M2" s="9">
+        <v>165</v>
+      </c>
+      <c r="N2" s="10"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="10">
-        <v>165</v>
-      </c>
-      <c r="M2" s="10">
-        <v>165</v>
-      </c>
-      <c r="N2" s="11"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="11">
         <v>60</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -53967,7 +53959,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="8">
         <v>1</v>
@@ -53983,25 +53975,25 @@
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="9">
         <v>1</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
-      <c r="Q3" s="12">
+      <c r="Q3" s="11">
         <v>60</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="8">
         <v>2</v>
       </c>
@@ -54015,7 +54007,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="8">
         <v>1</v>
@@ -54031,25 +54023,25 @@
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>30</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="11">
         <v>60</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="8">
         <v>3</v>
       </c>
@@ -54063,7 +54055,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" s="8">
         <v>1</v>
@@ -54084,16 +54076,16 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
-      <c r="Q5" s="12">
+      <c r="Q5" s="11">
         <v>60</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="8">
         <v>4</v>
       </c>
@@ -54107,7 +54099,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -54123,12 +54115,12 @@
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>1</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <v>1</v>
       </c>
       <c r="N6" s="3"/>
@@ -54151,7 +54143,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1">
         <v>0.8</v>
@@ -54166,13 +54158,13 @@
         <v>1</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="13" t="s">
-        <v>29</v>
+      <c r="K7" s="12" t="s">
+        <v>28</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="13">
         <v>100</v>
       </c>
-      <c r="M7" s="15"/>
+      <c r="M7" s="14"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="6"/>
@@ -54190,17 +54182,17 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="13" t="s">
-        <v>30</v>
+      <c r="K8" s="12" t="s">
+        <v>29</v>
       </c>
-      <c r="L8" s="14">
-        <v>50</v>
+      <c r="L8" s="13">
+        <v>100</v>
       </c>
-      <c r="M8" s="15"/>
+      <c r="M8" s="14"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-      <c r="Q8" s="15"/>
+      <c r="Q8" s="14"/>
       <c r="R8" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
@@ -54214,17 +54206,17 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="15"/>
+      <c r="M9" s="14"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="15"/>
+      <c r="Q9" s="14"/>
       <c r="R9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
@@ -54238,15 +54230,15 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="16" t="s">
-        <v>33</v>
+      <c r="K10" s="12"/>
+      <c r="L10" s="15" t="s">
+        <v>32</v>
       </c>
-      <c r="M10" s="15"/>
+      <c r="M10" s="14"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-      <c r="Q10" s="15"/>
+      <c r="Q10" s="14"/>
       <c r="R10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
@@ -54261,12 +54253,12 @@
       <c r="I11" s="1"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="14"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="Q11" s="15"/>
+      <c r="Q11" s="14"/>
       <c r="R11" s="3"/>
     </row>
   </sheetData>
